--- a/today_race2.xlsx
+++ b/today_race2.xlsx
@@ -61,55 +61,54 @@
     <t>単勝</t>
   </si>
   <si>
-    <t>キャントウェイト</t>
-  </si>
-  <si>
-    <t>ワイドエンペラー</t>
-  </si>
-  <si>
-    <t>リビアングラス</t>
-  </si>
-  <si>
-    <t>ヴーレヴー</t>
-  </si>
-  <si>
-    <t>アスクドゥポルテ</t>
-  </si>
-  <si>
-    <t>パンジャ</t>
-  </si>
-  <si>
-    <t>レガレイラ</t>
-  </si>
-  <si>
-    <t>メイショウゲキリン</t>
-  </si>
-  <si>
-    <t>コスモキュランダ</t>
-  </si>
-  <si>
-    <t>コスモブッドレア</t>
-  </si>
-  <si>
-    <t>セイウンプラチナ</t>
-  </si>
-  <si>
-    <t>エセルフリーダ</t>
-  </si>
-  <si>
-    <t>ジューンテイク</t>
+    <t>アルビオンライズ</t>
+  </si>
+  <si>
+    <t>トパーズヘッド</t>
+  </si>
+  <si>
+    <t>アンミツ</t>
+  </si>
+  <si>
+    <t>リコルディオーロ</t>
+  </si>
+  <si>
+    <t>コウソクレムリア</t>
+  </si>
+  <si>
+    <t>クリアマインド</t>
+  </si>
+  <si>
+    <t>ヴァンデエス</t>
+  </si>
+  <si>
+    <t>スヴァラ</t>
+  </si>
+  <si>
+    <t>アイビーカイロス</t>
+  </si>
+  <si>
+    <t>ハイトラクション</t>
+  </si>
+  <si>
+    <t>ハクタカ</t>
+  </si>
+  <si>
+    <t>アーバーバイティ</t>
+  </si>
+  <si>
+    <t>ファイアリーボルト</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -731,7 +730,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyBorder="1">
       <alignment vertical="center"/>
@@ -747,9 +746,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -1182,574 +1178,535 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="6">
-        <v>202606040611</v>
-      </c>
-      <c r="B2" s="7">
+        <v>202606040801</v>
+      </c>
+      <c r="B2" s="6">
         <v>1</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="7">
-        <v>57</v>
-      </c>
-      <c r="E2" s="7">
-        <v>19.1</v>
-      </c>
-      <c r="F2" s="7">
-        <v>19</v>
-      </c>
-      <c r="G2" s="8">
-        <v>98</v>
-      </c>
-      <c r="H2" s="7">
-        <v>26</v>
-      </c>
-      <c r="I2" s="8">
-        <v>95</v>
-      </c>
-      <c r="J2" s="7">
-        <v>-5</v>
-      </c>
-      <c r="K2" s="7">
+      <c r="D2" s="6">
+        <v>55</v>
+      </c>
+      <c r="E2" s="6">
+        <v>75</v>
+      </c>
+      <c r="F2" s="6">
+        <v>62</v>
+      </c>
+      <c r="G2" s="7">
+        <v>66</v>
+      </c>
+      <c r="H2" s="6">
+        <v>0</v>
+      </c>
+      <c r="I2" s="7">
+        <v>66</v>
+      </c>
+      <c r="J2" s="6">
+        <v>0</v>
+      </c>
+      <c r="K2" s="6">
         <v>1</v>
       </c>
       <c r="L2"/>
-      <c r="M2"/>
-      <c r="N2" s="7">
-        <v>7</v>
-      </c>
-      <c r="O2" s="7">
-        <v>19.9</v>
+      <c r="M2" s="6">
+        <v>1</v>
+      </c>
+      <c r="N2" s="6">
+        <v>1</v>
+      </c>
+      <c r="O2" s="6">
+        <v>2.3</v>
       </c>
       <c r="Q2" s="2"/>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="6">
-        <v>202606040611</v>
-      </c>
-      <c r="B3" s="7">
+        <v>202606040801</v>
+      </c>
+      <c r="B3" s="6">
         <v>2</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="7">
-        <v>57</v>
-      </c>
-      <c r="E3" s="7">
-        <v>8.3</v>
-      </c>
-      <c r="F3" s="7">
-        <v>8</v>
-      </c>
-      <c r="G3" s="8">
-        <v>90</v>
-      </c>
-      <c r="H3" s="7">
-        <v>-77</v>
-      </c>
-      <c r="I3" s="8">
-        <v>97</v>
-      </c>
-      <c r="J3" s="7">
-        <v>-13</v>
+      <c r="D3" s="6">
+        <v>55</v>
+      </c>
+      <c r="E3" s="6">
+        <v>6.8</v>
+      </c>
+      <c r="F3" s="6">
+        <v>10</v>
+      </c>
+      <c r="G3" s="7">
+        <v>47</v>
+      </c>
+      <c r="H3" s="6">
+        <v>-81</v>
+      </c>
+      <c r="I3" s="7">
+        <v>47</v>
+      </c>
+      <c r="J3" s="6">
+        <v>-81</v>
       </c>
       <c r="K3"/>
       <c r="L3"/>
       <c r="M3"/>
-      <c r="N3" s="7">
-        <v>10</v>
-      </c>
-      <c r="O3" s="7">
-        <v>36.6</v>
+      <c r="N3" s="6">
+        <v>13</v>
+      </c>
+      <c r="O3" s="6">
+        <v>97.8</v>
       </c>
       <c r="Q3" s="2"/>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="6">
-        <v>202606040611</v>
-      </c>
-      <c r="B4" s="7">
+        <v>202606040801</v>
+      </c>
+      <c r="B4" s="6">
         <v>3</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="7">
-        <v>57</v>
-      </c>
-      <c r="E4" s="7">
-        <v>10.8</v>
-      </c>
-      <c r="F4" s="7">
-        <v>12</v>
-      </c>
-      <c r="G4" s="8">
-        <v>92</v>
-      </c>
-      <c r="H4" s="7">
-        <v>16</v>
-      </c>
-      <c r="I4" s="8">
-        <v>97</v>
-      </c>
-      <c r="J4" s="7">
-        <v>-69</v>
-      </c>
+      <c r="D4" s="6">
+        <v>53</v>
+      </c>
+      <c r="E4" s="6">
+        <v>15.6</v>
+      </c>
+      <c r="F4" s="6">
+        <v>19</v>
+      </c>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
       <c r="K4"/>
-      <c r="L4" s="7">
+      <c r="L4"/>
+      <c r="M4" s="6">
         <v>1</v>
       </c>
-      <c r="M4" s="7">
-        <v>1</v>
-      </c>
-      <c r="N4" s="7">
-        <v>8</v>
-      </c>
-      <c r="O4" s="7">
-        <v>31</v>
+      <c r="N4" s="6">
+        <v>3</v>
+      </c>
+      <c r="O4" s="6">
+        <v>6.6</v>
       </c>
       <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="6">
-        <v>202606040611</v>
-      </c>
-      <c r="B5" s="7">
+        <v>202606040801</v>
+      </c>
+      <c r="B5" s="6">
         <v>4</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="7">
-        <v>55</v>
-      </c>
-      <c r="E5" s="7">
-        <v>33</v>
-      </c>
-      <c r="F5" s="7">
-        <v>25</v>
-      </c>
-      <c r="G5" s="8">
-        <v>106</v>
-      </c>
-      <c r="H5" s="7">
+      <c r="D5" s="6">
+        <v>52</v>
+      </c>
+      <c r="E5" s="6">
+        <v>47.6</v>
+      </c>
+      <c r="F5" s="6">
         <v>36</v>
       </c>
-      <c r="I5" s="8">
-        <v>104</v>
-      </c>
-      <c r="J5" s="7">
-        <v>77</v>
+      <c r="G5" s="7">
+        <v>58</v>
+      </c>
+      <c r="H5" s="6">
+        <v>34</v>
+      </c>
+      <c r="I5" s="7">
+        <v>50</v>
+      </c>
+      <c r="J5" s="6">
+        <v>2</v>
       </c>
       <c r="K5"/>
-      <c r="L5" s="7">
+      <c r="L5"/>
+      <c r="M5" s="6">
         <v>1</v>
       </c>
-      <c r="M5"/>
-      <c r="N5" s="7">
-        <v>3</v>
-      </c>
-      <c r="O5" s="7">
-        <v>6.7</v>
+      <c r="N5" s="6">
+        <v>5</v>
+      </c>
+      <c r="O5" s="6">
+        <v>10.5</v>
       </c>
       <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="6">
-        <v>202606040611</v>
-      </c>
-      <c r="B6" s="7">
+        <v>202606040801</v>
+      </c>
+      <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="7">
-        <v>57</v>
-      </c>
-      <c r="E6" s="7">
-        <v>5.8</v>
-      </c>
-      <c r="F6" s="7">
-        <v>3</v>
-      </c>
-      <c r="G6" s="8">
-        <v>83</v>
-      </c>
-      <c r="H6" s="7">
-        <v>-56</v>
-      </c>
-      <c r="I6" s="8">
-        <v>77</v>
-      </c>
-      <c r="J6" s="7">
-        <v>-122</v>
-      </c>
+      <c r="D6" s="6">
+        <v>55</v>
+      </c>
+      <c r="E6" s="6">
+        <v>21.2</v>
+      </c>
+      <c r="F6" s="6">
+        <v>21</v>
+      </c>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
       <c r="K6"/>
       <c r="L6"/>
       <c r="M6"/>
-      <c r="N6" s="7">
-        <v>11</v>
-      </c>
-      <c r="O6" s="7">
-        <v>94.2</v>
+      <c r="N6" s="6">
+        <v>6</v>
+      </c>
+      <c r="O6" s="6">
+        <v>15.7</v>
       </c>
       <c r="Q6" s="2"/>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="6">
-        <v>202606040611</v>
-      </c>
-      <c r="B7" s="7">
+        <v>202606040801</v>
+      </c>
+      <c r="B7" s="6">
         <v>6</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="7">
-        <v>57</v>
-      </c>
-      <c r="E7" s="7">
-        <v>22.1</v>
-      </c>
-      <c r="F7" s="7">
-        <v>22</v>
-      </c>
-      <c r="G7" s="8">
-        <v>100</v>
-      </c>
-      <c r="H7" s="7">
-        <v>54</v>
-      </c>
-      <c r="I7" s="8">
-        <v>96</v>
-      </c>
-      <c r="J7" s="7">
-        <v>-31</v>
-      </c>
-      <c r="K7" s="7">
-        <v>1</v>
-      </c>
+      <c r="D7" s="6">
+        <v>55</v>
+      </c>
+      <c r="E7" s="6">
+        <v>5.7</v>
+      </c>
+      <c r="F7" s="6">
+        <v>7</v>
+      </c>
+      <c r="G7" s="7">
+        <v>20</v>
+      </c>
+      <c r="H7" s="6">
+        <v>-195</v>
+      </c>
+      <c r="I7" s="7">
+        <v>20</v>
+      </c>
+      <c r="J7" s="6">
+        <v>-195</v>
+      </c>
+      <c r="K7"/>
       <c r="L7"/>
       <c r="M7"/>
-      <c r="N7" s="7">
-        <v>6</v>
-      </c>
-      <c r="O7" s="7">
-        <v>14.3</v>
+      <c r="N7" s="6">
+        <v>11</v>
+      </c>
+      <c r="O7" s="6">
+        <v>47.7</v>
       </c>
       <c r="Q7" s="2"/>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="6">
-        <v>202606040611</v>
-      </c>
-      <c r="B8" s="7">
+        <v>202606040801</v>
+      </c>
+      <c r="B8" s="6">
         <v>7</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="7">
-        <v>56</v>
-      </c>
-      <c r="E8" s="7">
-        <v>74.3</v>
-      </c>
-      <c r="F8" s="7">
-        <v>53</v>
-      </c>
-      <c r="G8" s="8">
-        <v>87</v>
-      </c>
-      <c r="H8" s="7">
-        <v>-39</v>
-      </c>
-      <c r="I8" s="8">
-        <v>108</v>
-      </c>
-      <c r="J8" s="7">
-        <v>38</v>
-      </c>
-      <c r="K8" s="7">
-        <v>1</v>
-      </c>
+      <c r="D8" s="6">
+        <v>55</v>
+      </c>
+      <c r="E8" s="6">
+        <v>6.7</v>
+      </c>
+      <c r="F8" s="6">
+        <v>10</v>
+      </c>
+      <c r="G8" s="7">
+        <v>44</v>
+      </c>
+      <c r="H8" s="6">
+        <v>-130</v>
+      </c>
+      <c r="I8" s="7">
+        <v>44</v>
+      </c>
+      <c r="J8" s="6">
+        <v>-130</v>
+      </c>
+      <c r="K8"/>
       <c r="L8"/>
       <c r="M8"/>
-      <c r="N8" s="7">
-        <v>1</v>
-      </c>
-      <c r="O8" s="7">
-        <v>2.7</v>
+      <c r="N8" s="6">
+        <v>12</v>
+      </c>
+      <c r="O8" s="6">
+        <v>94.7</v>
       </c>
       <c r="Q8" s="2"/>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="6">
-        <v>202606040611</v>
-      </c>
-      <c r="B9" s="7">
+        <v>202606040801</v>
+      </c>
+      <c r="B9" s="6">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="7">
-        <v>57</v>
-      </c>
-      <c r="E9" s="7">
-        <v>6.7</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="D9" s="6">
+        <v>55</v>
+      </c>
+      <c r="E9" s="6">
+        <v>4.5</v>
+      </c>
+      <c r="F9" s="6">
         <v>6</v>
       </c>
-      <c r="G9" s="8">
-        <v>88</v>
-      </c>
-      <c r="H9" s="7">
-        <v>45</v>
-      </c>
-      <c r="I9" s="8">
-        <v>88</v>
-      </c>
-      <c r="J9" s="7">
-        <v>45</v>
-      </c>
-      <c r="K9"/>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9" s="6">
+        <v>1</v>
+      </c>
       <c r="L9"/>
-      <c r="M9" s="7">
-        <v>1</v>
-      </c>
-      <c r="N9" s="7">
-        <v>9</v>
-      </c>
-      <c r="O9" s="7">
-        <v>35.5</v>
+      <c r="M9"/>
+      <c r="N9" s="6">
+        <v>10</v>
+      </c>
+      <c r="O9" s="6">
+        <v>37.8</v>
       </c>
       <c r="Q9" s="2"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="6">
-        <v>202606040611</v>
-      </c>
-      <c r="B10" s="7">
+        <v>202606040801</v>
+      </c>
+      <c r="B10" s="6">
         <v>9</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="7">
-        <v>57</v>
-      </c>
-      <c r="E10" s="7">
-        <v>63.5</v>
-      </c>
-      <c r="F10" s="7">
-        <v>43</v>
-      </c>
-      <c r="G10" s="8">
-        <v>96</v>
-      </c>
-      <c r="H10" s="7">
-        <v>28</v>
-      </c>
-      <c r="I10" s="8">
-        <v>103</v>
-      </c>
-      <c r="J10" s="7">
-        <v>9</v>
+      <c r="D10" s="6">
+        <v>55</v>
+      </c>
+      <c r="E10" s="6">
+        <v>25.6</v>
+      </c>
+      <c r="F10" s="6">
+        <v>30</v>
+      </c>
+      <c r="G10" s="7">
+        <v>33</v>
+      </c>
+      <c r="H10" s="6">
+        <v>-39</v>
+      </c>
+      <c r="I10" s="7">
+        <v>33</v>
+      </c>
+      <c r="J10" s="6">
+        <v>-39</v>
       </c>
       <c r="K10"/>
-      <c r="L10" s="7">
+      <c r="L10"/>
+      <c r="M10" s="6">
         <v>1</v>
       </c>
-      <c r="M10" s="7">
-        <v>1</v>
-      </c>
-      <c r="N10" s="7">
-        <v>2</v>
-      </c>
-      <c r="O10" s="7">
-        <v>3.2</v>
+      <c r="N10" s="6">
+        <v>4</v>
+      </c>
+      <c r="O10" s="6">
+        <v>7.7</v>
       </c>
       <c r="Q10" s="2"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="6">
-        <v>202606040611</v>
-      </c>
-      <c r="B11" s="7">
+        <v>202606040801</v>
+      </c>
+      <c r="B11" s="6">
         <v>10</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="7">
-        <v>57</v>
-      </c>
-      <c r="E11" s="7">
-        <v>3.9</v>
-      </c>
-      <c r="F11" s="7">
-        <v>2</v>
-      </c>
-      <c r="G11" s="8">
-        <v>77</v>
-      </c>
-      <c r="H11" s="7">
-        <v>-139</v>
-      </c>
-      <c r="I11" s="8">
-        <v>82</v>
-      </c>
-      <c r="J11" s="7">
-        <v>-81</v>
+      <c r="D11" s="6">
+        <v>54</v>
+      </c>
+      <c r="E11" s="6">
+        <v>9</v>
+      </c>
+      <c r="F11" s="6">
+        <v>4</v>
+      </c>
+      <c r="G11" s="7">
+        <v>53</v>
+      </c>
+      <c r="H11" s="6">
+        <v>-192</v>
+      </c>
+      <c r="I11" s="7">
+        <v>24</v>
+      </c>
+      <c r="J11" s="6">
+        <v>-453</v>
       </c>
       <c r="K11"/>
       <c r="L11"/>
       <c r="M11"/>
-      <c r="N11" s="7">
-        <v>12</v>
-      </c>
-      <c r="O11" s="7">
-        <v>106.7</v>
+      <c r="N11" s="6">
+        <v>7</v>
+      </c>
+      <c r="O11" s="6">
+        <v>25.3</v>
       </c>
       <c r="Q11" s="2"/>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="6">
-        <v>202606040611</v>
-      </c>
-      <c r="B12" s="7">
+        <v>202606040801</v>
+      </c>
+      <c r="B12" s="6">
         <v>11</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="7">
-        <v>57</v>
-      </c>
-      <c r="E12" s="7">
-        <v>9.8</v>
-      </c>
-      <c r="F12" s="7">
-        <v>2</v>
-      </c>
-      <c r="G12" s="8">
-        <v>84</v>
-      </c>
-      <c r="H12" s="7">
-        <v>-135</v>
-      </c>
-      <c r="I12" s="8">
-        <v>102</v>
-      </c>
-      <c r="J12" s="7">
-        <v>-30</v>
-      </c>
+      <c r="D12" s="6">
+        <v>55</v>
+      </c>
+      <c r="E12" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="F12" s="6">
+        <v>5</v>
+      </c>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
       <c r="K12"/>
       <c r="L12"/>
-      <c r="M12" s="7">
-        <v>1</v>
-      </c>
-      <c r="N12" s="7">
-        <v>13</v>
-      </c>
-      <c r="O12" s="7">
-        <v>107.4</v>
+      <c r="M12"/>
+      <c r="N12" s="6">
+        <v>9</v>
+      </c>
+      <c r="O12" s="6">
+        <v>33.3</v>
       </c>
       <c r="Q12" s="2"/>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="6">
-        <v>202606040611</v>
-      </c>
-      <c r="B13" s="7">
+        <v>202606040801</v>
+      </c>
+      <c r="B13" s="6">
         <v>12</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="6">
         <v>55</v>
       </c>
-      <c r="E13" s="7">
-        <v>13.5</v>
-      </c>
-      <c r="F13" s="7">
-        <v>22</v>
-      </c>
-      <c r="G13" s="8">
-        <v>96</v>
-      </c>
-      <c r="H13" s="7">
-        <v>24</v>
-      </c>
-      <c r="I13" s="8">
-        <v>97</v>
-      </c>
-      <c r="J13" s="7">
-        <v>35</v>
-      </c>
-      <c r="K13"/>
-      <c r="L13" s="7">
+      <c r="E13" s="6">
+        <v>55.4</v>
+      </c>
+      <c r="F13" s="6">
+        <v>46</v>
+      </c>
+      <c r="G13" s="7">
+        <v>63</v>
+      </c>
+      <c r="H13" s="6">
+        <v>-18</v>
+      </c>
+      <c r="I13" s="7">
+        <v>63</v>
+      </c>
+      <c r="J13" s="6">
+        <v>-18</v>
+      </c>
+      <c r="K13" s="6">
         <v>1</v>
       </c>
-      <c r="M13"/>
-      <c r="N13" s="7">
-        <v>5</v>
-      </c>
-      <c r="O13" s="7">
-        <v>10.9</v>
+      <c r="L13"/>
+      <c r="M13" s="6">
+        <v>1</v>
+      </c>
+      <c r="N13" s="6">
+        <v>2</v>
+      </c>
+      <c r="O13" s="6">
+        <v>4.6</v>
       </c>
       <c r="Q13" s="2"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="6">
-        <v>202606040611</v>
-      </c>
-      <c r="B14" s="7">
+        <v>202606040801</v>
+      </c>
+      <c r="B14" s="6">
         <v>13</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="7">
-        <v>58</v>
-      </c>
-      <c r="E14" s="7">
-        <v>29.3</v>
-      </c>
-      <c r="F14" s="7">
-        <v>21</v>
-      </c>
-      <c r="G14" s="8">
-        <v>87</v>
-      </c>
-      <c r="H14" s="7">
-        <v>-72</v>
-      </c>
-      <c r="I14" s="8">
-        <v>110</v>
-      </c>
-      <c r="J14" s="7">
-        <v>32</v>
+      <c r="D14" s="6">
+        <v>55</v>
+      </c>
+      <c r="E14" s="6">
+        <v>21.4</v>
+      </c>
+      <c r="F14" s="6">
+        <v>25</v>
+      </c>
+      <c r="G14" s="7">
+        <v>53</v>
+      </c>
+      <c r="H14" s="6">
+        <v>16</v>
+      </c>
+      <c r="I14" s="7">
+        <v>53</v>
+      </c>
+      <c r="J14" s="6">
+        <v>16</v>
       </c>
       <c r="K14"/>
-      <c r="L14" s="7">
-        <v>1</v>
-      </c>
+      <c r="L14"/>
       <c r="M14"/>
-      <c r="N14" s="7">
-        <v>4</v>
-      </c>
-      <c r="O14" s="7">
-        <v>9.8</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15">
+      <c r="N14" s="6">
+        <v>8</v>
+      </c>
+      <c r="O14" s="6">
+        <v>32.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15"/>
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15"/>
@@ -1765,7 +1722,8 @@
       <c r="N15"/>
       <c r="O15"/>
     </row>
-    <row r="16" spans="2:15">
+    <row r="16" spans="1:15">
+      <c r="A16"/>
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -1781,7 +1739,8 @@
       <c r="N16"/>
       <c r="O16"/>
     </row>
-    <row r="17" spans="2:15">
+    <row r="17" spans="1:15">
+      <c r="A17"/>
       <c r="B17"/>
       <c r="C17"/>
       <c r="D17"/>
@@ -1797,7 +1756,8 @@
       <c r="N17"/>
       <c r="O17"/>
     </row>
-    <row r="18" spans="2:15">
+    <row r="18" spans="1:15">
+      <c r="A18"/>
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18"/>
@@ -1813,7 +1773,8 @@
       <c r="N18"/>
       <c r="O18"/>
     </row>
-    <row r="19" spans="2:15">
+    <row r="19" spans="1:15">
+      <c r="A19"/>
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
@@ -1830,116 +1791,116 @@
       <c r="O19"/>
     </row>
     <row r="20" spans="2:15">
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="8"/>
       <c r="K20"/>
       <c r="L20"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
     </row>
     <row r="21" spans="2:15">
-      <c r="B21" s="9"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
       <c r="L21"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
     </row>
     <row r="22" spans="2:15">
-      <c r="B22" s="9"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="8"/>
       <c r="K22"/>
       <c r="L22"/>
       <c r="M22"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
     </row>
     <row r="23" spans="2:15">
-      <c r="B23" s="9"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
       <c r="L23"/>
       <c r="M23"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
     </row>
     <row r="24" spans="2:15">
-      <c r="B24" s="9"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="8"/>
       <c r="K24"/>
       <c r="L24"/>
       <c r="M24"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
     </row>
     <row r="25" spans="2:15">
-      <c r="B25" s="9"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="8"/>
       <c r="K25"/>
       <c r="L25"/>
       <c r="M25"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
     </row>
     <row r="26" spans="2:15">
-      <c r="B26" s="9"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="9"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="8"/>
       <c r="K26"/>
       <c r="L26"/>
       <c r="M26"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
     </row>
     <row r="27" spans="2:15">
       <c r="B27"/>

--- a/today_race2.xlsx
+++ b/today_race2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>レースID</t>
   </si>
@@ -98,6 +98,42 @@
   </si>
   <si>
     <t>ファイアリーボルト</t>
+  </si>
+  <si>
+    <t>ブラックナザレ</t>
+  </si>
+  <si>
+    <t>マルスフィス</t>
+  </si>
+  <si>
+    <t>ニーナラルゴ</t>
+  </si>
+  <si>
+    <t>タッカーヴィーチェ</t>
+  </si>
+  <si>
+    <t>オシゴリ</t>
+  </si>
+  <si>
+    <t>リオンパリス</t>
+  </si>
+  <si>
+    <t>サムワンユーラヴド</t>
+  </si>
+  <si>
+    <t>ウィルステート</t>
+  </si>
+  <si>
+    <t>エコロテラ</t>
+  </si>
+  <si>
+    <t>ヴェントリナ</t>
+  </si>
+  <si>
+    <t>ハンサム</t>
+  </si>
+  <si>
+    <t>リキマル</t>
   </si>
 </sst>
 </file>
@@ -730,7 +766,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyBorder="1">
       <alignment vertical="center"/>
@@ -746,12 +782,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -1706,203 +1736,511 @@
       </c>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15"/>
-      <c r="B15"/>
-      <c r="C15"/>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15"/>
-      <c r="H15"/>
-      <c r="I15"/>
-      <c r="J15"/>
+      <c r="A15" s="6">
+        <v>202606040802</v>
+      </c>
+      <c r="B15" s="6">
+        <v>1</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="6">
+        <v>55</v>
+      </c>
+      <c r="E15" s="6">
+        <v>5.9</v>
+      </c>
+      <c r="F15" s="6">
+        <v>4</v>
+      </c>
+      <c r="G15" s="7">
+        <v>52</v>
+      </c>
+      <c r="H15" s="6">
+        <v>-6</v>
+      </c>
+      <c r="I15" s="7">
+        <v>52</v>
+      </c>
+      <c r="J15" s="6">
+        <v>-6</v>
+      </c>
       <c r="K15"/>
       <c r="L15"/>
       <c r="M15"/>
-      <c r="N15"/>
-      <c r="O15"/>
+      <c r="N15" s="6">
+        <v>11</v>
+      </c>
+      <c r="O15" s="6">
+        <v>78.9</v>
+      </c>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16"/>
-      <c r="B16"/>
-      <c r="C16"/>
-      <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16"/>
+      <c r="A16" s="6">
+        <v>202606040802</v>
+      </c>
+      <c r="B16" s="6">
+        <v>2</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="6">
+        <v>55</v>
+      </c>
+      <c r="E16" s="6">
+        <v>6.9</v>
+      </c>
+      <c r="F16" s="6">
+        <v>12</v>
+      </c>
+      <c r="G16" s="7">
+        <v>51</v>
+      </c>
+      <c r="H16" s="6">
+        <v>-26</v>
+      </c>
+      <c r="I16" s="7">
+        <v>51</v>
+      </c>
+      <c r="J16" s="6">
+        <v>-26</v>
+      </c>
       <c r="K16"/>
       <c r="L16"/>
       <c r="M16"/>
-      <c r="N16"/>
-      <c r="O16"/>
+      <c r="N16" s="6">
+        <v>9</v>
+      </c>
+      <c r="O16" s="6">
+        <v>37.9</v>
+      </c>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17"/>
-      <c r="B17"/>
-      <c r="C17"/>
-      <c r="D17"/>
-      <c r="E17"/>
-      <c r="F17"/>
-      <c r="G17"/>
-      <c r="H17"/>
-      <c r="I17"/>
-      <c r="J17"/>
+      <c r="A17" s="6">
+        <v>202606040802</v>
+      </c>
+      <c r="B17" s="6">
+        <v>3</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="6">
+        <v>55</v>
+      </c>
+      <c r="E17" s="6">
+        <v>51.5</v>
+      </c>
+      <c r="F17" s="6">
+        <v>32</v>
+      </c>
+      <c r="G17" s="7">
+        <v>76</v>
+      </c>
+      <c r="H17" s="6">
+        <v>24</v>
+      </c>
+      <c r="I17" s="7">
+        <v>67</v>
+      </c>
+      <c r="J17" s="6">
+        <v>45</v>
+      </c>
       <c r="K17"/>
       <c r="L17"/>
-      <c r="M17"/>
-      <c r="N17"/>
-      <c r="O17"/>
+      <c r="M17" s="6">
+        <v>1</v>
+      </c>
+      <c r="N17" s="6">
+        <v>2</v>
+      </c>
+      <c r="O17" s="6">
+        <v>4.2</v>
+      </c>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18"/>
-      <c r="B18"/>
-      <c r="C18"/>
-      <c r="D18"/>
-      <c r="E18"/>
-      <c r="F18"/>
-      <c r="G18"/>
-      <c r="H18"/>
-      <c r="I18"/>
-      <c r="J18"/>
+      <c r="A18" s="6">
+        <v>202606040802</v>
+      </c>
+      <c r="B18" s="6">
+        <v>4</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="6">
+        <v>55</v>
+      </c>
+      <c r="E18" s="6">
+        <v>21.4</v>
+      </c>
+      <c r="F18" s="6">
+        <v>26</v>
+      </c>
+      <c r="G18" s="7">
+        <v>73</v>
+      </c>
+      <c r="H18" s="6">
+        <v>11</v>
+      </c>
+      <c r="I18" s="7">
+        <v>73</v>
+      </c>
+      <c r="J18" s="6">
+        <v>11</v>
+      </c>
       <c r="K18"/>
       <c r="L18"/>
       <c r="M18"/>
-      <c r="N18"/>
-      <c r="O18"/>
+      <c r="N18" s="6">
+        <v>7</v>
+      </c>
+      <c r="O18" s="6">
+        <v>34.3</v>
+      </c>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19"/>
-      <c r="B19"/>
-      <c r="C19"/>
-      <c r="D19"/>
-      <c r="E19"/>
-      <c r="F19"/>
-      <c r="G19"/>
-      <c r="H19"/>
-      <c r="I19"/>
-      <c r="J19"/>
+      <c r="A19" s="6">
+        <v>202606040802</v>
+      </c>
+      <c r="B19" s="6">
+        <v>5</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="6">
+        <v>55</v>
+      </c>
+      <c r="E19" s="6">
+        <v>5.3</v>
+      </c>
+      <c r="F19" s="6">
+        <v>6</v>
+      </c>
+      <c r="G19" s="7">
+        <v>61</v>
+      </c>
+      <c r="H19" s="6">
+        <v>-123</v>
+      </c>
+      <c r="I19" s="7">
+        <v>61</v>
+      </c>
+      <c r="J19" s="6">
+        <v>-123</v>
+      </c>
       <c r="K19"/>
       <c r="L19"/>
       <c r="M19"/>
-      <c r="N19"/>
-      <c r="O19"/>
-    </row>
-    <row r="20" spans="2:15">
-      <c r="B20" s="8"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="8"/>
+      <c r="N19" s="6">
+        <v>10</v>
+      </c>
+      <c r="O19" s="6">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="6">
+        <v>202606040802</v>
+      </c>
+      <c r="B20" s="6">
+        <v>6</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="6">
+        <v>55</v>
+      </c>
+      <c r="E20" s="6">
+        <v>4.2</v>
+      </c>
+      <c r="F20" s="6">
+        <v>4</v>
+      </c>
+      <c r="G20" s="7">
+        <v>27</v>
+      </c>
+      <c r="H20" s="6">
+        <v>-172</v>
+      </c>
+      <c r="I20" s="7">
+        <v>27</v>
+      </c>
+      <c r="J20" s="6">
+        <v>-172</v>
+      </c>
       <c r="K20"/>
       <c r="L20"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-    </row>
-    <row r="21" spans="2:15">
-      <c r="B21" s="8"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
+      <c r="M20"/>
+      <c r="N20" s="6">
+        <v>12</v>
+      </c>
+      <c r="O20" s="6">
+        <v>110.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" s="6">
+        <v>202606040802</v>
+      </c>
+      <c r="B21" s="6">
+        <v>7</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="6">
+        <v>53</v>
+      </c>
+      <c r="E21" s="6">
+        <v>10.6</v>
+      </c>
+      <c r="F21" s="6">
+        <v>20</v>
+      </c>
+      <c r="G21" s="7">
+        <v>46</v>
+      </c>
+      <c r="H21" s="6">
+        <v>8</v>
+      </c>
+      <c r="I21" s="7">
+        <v>46</v>
+      </c>
+      <c r="J21" s="6">
+        <v>8</v>
+      </c>
+      <c r="K21" s="6">
+        <v>1</v>
+      </c>
       <c r="L21"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-    </row>
-    <row r="22" spans="2:15">
-      <c r="B22" s="8"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="8"/>
+      <c r="M21"/>
+      <c r="N21" s="6">
+        <v>5</v>
+      </c>
+      <c r="O21" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="6">
+        <v>202606040802</v>
+      </c>
+      <c r="B22" s="6">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="6">
+        <v>55</v>
+      </c>
+      <c r="E22" s="6">
+        <v>57.8</v>
+      </c>
+      <c r="F22" s="6">
+        <v>40</v>
+      </c>
+      <c r="G22" s="7">
+        <v>65</v>
+      </c>
+      <c r="H22" s="6">
+        <v>31</v>
+      </c>
+      <c r="I22" s="7">
+        <v>65</v>
+      </c>
+      <c r="J22" s="6">
+        <v>31</v>
+      </c>
       <c r="K22"/>
       <c r="L22"/>
       <c r="M22"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
-    </row>
-    <row r="23" spans="2:15">
-      <c r="B23" s="8"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
+      <c r="N22" s="6">
+        <v>4</v>
+      </c>
+      <c r="O22" s="6">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="6">
+        <v>202606040802</v>
+      </c>
+      <c r="B23" s="6">
+        <v>9</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="6">
+        <v>55</v>
+      </c>
+      <c r="E23" s="6">
+        <v>12.7</v>
+      </c>
+      <c r="F23" s="6">
+        <v>14</v>
+      </c>
+      <c r="G23" s="7">
+        <v>73</v>
+      </c>
+      <c r="H23" s="6">
+        <v>31</v>
+      </c>
+      <c r="I23" s="7">
+        <v>29</v>
+      </c>
+      <c r="J23" s="6">
+        <v>-1</v>
+      </c>
+      <c r="K23"/>
       <c r="L23"/>
       <c r="M23"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="8"/>
-    </row>
-    <row r="24" spans="2:15">
-      <c r="B24" s="8"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="8"/>
-      <c r="K24"/>
+      <c r="N23" s="6">
+        <v>6</v>
+      </c>
+      <c r="O23" s="6">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="6">
+        <v>202606040802</v>
+      </c>
+      <c r="B24" s="6">
+        <v>10</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="6">
+        <v>55</v>
+      </c>
+      <c r="E24" s="6">
+        <v>58.7</v>
+      </c>
+      <c r="F24" s="6">
+        <v>34</v>
+      </c>
+      <c r="G24" s="7">
+        <v>77</v>
+      </c>
+      <c r="H24" s="6">
+        <v>-5</v>
+      </c>
+      <c r="I24" s="7">
+        <v>69</v>
+      </c>
+      <c r="J24" s="6">
+        <v>-10</v>
+      </c>
+      <c r="K24" s="6">
+        <v>1</v>
+      </c>
       <c r="L24"/>
-      <c r="M24"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-    </row>
-    <row r="25" spans="2:15">
-      <c r="B25" s="8"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="8"/>
-      <c r="K25"/>
+      <c r="M24" s="6">
+        <v>1</v>
+      </c>
+      <c r="N24" s="6">
+        <v>3</v>
+      </c>
+      <c r="O24" s="6">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="6">
+        <v>202606040802</v>
+      </c>
+      <c r="B25" s="6">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="6">
+        <v>55</v>
+      </c>
+      <c r="E25" s="6">
+        <v>57</v>
+      </c>
+      <c r="F25" s="6">
+        <v>42</v>
+      </c>
+      <c r="G25" s="7">
+        <v>87</v>
+      </c>
+      <c r="H25" s="6">
+        <v>0</v>
+      </c>
+      <c r="I25" s="7">
+        <v>87</v>
+      </c>
+      <c r="J25" s="6">
+        <v>0</v>
+      </c>
+      <c r="K25" s="6">
+        <v>1</v>
+      </c>
       <c r="L25"/>
-      <c r="M25"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
-    </row>
-    <row r="26" spans="2:15">
-      <c r="B26" s="8"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="8"/>
+      <c r="M25" s="6">
+        <v>1</v>
+      </c>
+      <c r="N25" s="6">
+        <v>1</v>
+      </c>
+      <c r="O25" s="6">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="6">
+        <v>202606040802</v>
+      </c>
+      <c r="B26" s="6">
+        <v>12</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" s="6">
+        <v>55</v>
+      </c>
+      <c r="E26" s="6">
+        <v>8.1</v>
+      </c>
+      <c r="F26" s="6">
+        <v>13</v>
+      </c>
+      <c r="G26" s="7">
+        <v>63</v>
+      </c>
+      <c r="H26" s="6">
+        <v>-85</v>
+      </c>
+      <c r="I26" s="7">
+        <v>63</v>
+      </c>
+      <c r="J26" s="6">
+        <v>-85</v>
+      </c>
       <c r="K26"/>
       <c r="L26"/>
       <c r="M26"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
-    </row>
-    <row r="27" spans="2:15">
+      <c r="N26" s="6">
+        <v>8</v>
+      </c>
+      <c r="O26" s="6">
+        <v>36.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27"/>
       <c r="B27"/>
       <c r="C27"/>
       <c r="D27"/>
@@ -1918,7 +2256,8 @@
       <c r="N27"/>
       <c r="O27"/>
     </row>
-    <row r="28" spans="2:15">
+    <row r="28" spans="1:15">
+      <c r="A28"/>
       <c r="B28"/>
       <c r="C28"/>
       <c r="D28"/>
@@ -1934,7 +2273,8 @@
       <c r="N28"/>
       <c r="O28"/>
     </row>
-    <row r="29" spans="2:15">
+    <row r="29" spans="1:15">
+      <c r="A29"/>
       <c r="B29"/>
       <c r="C29"/>
       <c r="D29"/>
@@ -1950,7 +2290,8 @@
       <c r="N29"/>
       <c r="O29"/>
     </row>
-    <row r="30" spans="2:15">
+    <row r="30" spans="1:15">
+      <c r="A30"/>
       <c r="B30"/>
       <c r="C30"/>
       <c r="D30"/>
@@ -1966,7 +2307,8 @@
       <c r="N30"/>
       <c r="O30"/>
     </row>
-    <row r="31" spans="2:15">
+    <row r="31" spans="1:15">
+      <c r="A31"/>
       <c r="B31"/>
       <c r="C31"/>
       <c r="D31"/>
@@ -1982,7 +2324,8 @@
       <c r="N31"/>
       <c r="O31"/>
     </row>
-    <row r="32" spans="2:15">
+    <row r="32" spans="1:15">
+      <c r="A32"/>
       <c r="B32"/>
       <c r="C32"/>
       <c r="D32"/>

--- a/today_race2.xlsx
+++ b/today_race2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>レースID</t>
   </si>
@@ -134,6 +134,54 @@
   </si>
   <si>
     <t>リキマル</t>
+  </si>
+  <si>
+    <t>ロイヤルグルーヴ</t>
+  </si>
+  <si>
+    <t>ドナミモザ</t>
+  </si>
+  <si>
+    <t>モルスリール</t>
+  </si>
+  <si>
+    <t>コパノキラキラ</t>
+  </si>
+  <si>
+    <t>プラチナリーフ</t>
+  </si>
+  <si>
+    <t>ブリッド</t>
+  </si>
+  <si>
+    <t>スパーキー</t>
+  </si>
+  <si>
+    <t>ブルーサンタ</t>
+  </si>
+  <si>
+    <t>ツイストマインド</t>
+  </si>
+  <si>
+    <t>セイトゥゴールド</t>
+  </si>
+  <si>
+    <t>オレガイチバンイイ</t>
+  </si>
+  <si>
+    <t>ゼットターム</t>
+  </si>
+  <si>
+    <t>ボスヒッツ</t>
+  </si>
+  <si>
+    <t>アイビーナツユメ</t>
+  </si>
+  <si>
+    <t>ジェイエルバージ</t>
+  </si>
+  <si>
+    <t>ココル</t>
   </si>
 </sst>
 </file>
@@ -1139,7 +1187,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="17.5555555555556" style="1" customWidth="1"/>
@@ -2240,12 +2288,24 @@
       </c>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27"/>
-      <c r="B27"/>
-      <c r="C27"/>
-      <c r="D27"/>
-      <c r="E27"/>
-      <c r="F27"/>
+      <c r="A27" s="6">
+        <v>202606040803</v>
+      </c>
+      <c r="B27" s="6">
+        <v>1</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="6">
+        <v>53</v>
+      </c>
+      <c r="E27" s="6">
+        <v>5.2</v>
+      </c>
+      <c r="F27" s="6">
+        <v>8</v>
+      </c>
       <c r="G27"/>
       <c r="H27"/>
       <c r="I27"/>
@@ -2257,12 +2317,24 @@
       <c r="O27"/>
     </row>
     <row r="28" spans="1:15">
-      <c r="A28"/>
-      <c r="B28"/>
-      <c r="C28"/>
-      <c r="D28"/>
-      <c r="E28"/>
-      <c r="F28"/>
+      <c r="A28" s="6">
+        <v>202606040803</v>
+      </c>
+      <c r="B28" s="6">
+        <v>2</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" s="6">
+        <v>54</v>
+      </c>
+      <c r="E28" s="6">
+        <v>5.4</v>
+      </c>
+      <c r="F28" s="6">
+        <v>10</v>
+      </c>
       <c r="G28"/>
       <c r="H28"/>
       <c r="I28"/>
@@ -2274,12 +2346,24 @@
       <c r="O28"/>
     </row>
     <row r="29" spans="1:15">
-      <c r="A29"/>
-      <c r="B29"/>
-      <c r="C29"/>
-      <c r="D29"/>
-      <c r="E29"/>
-      <c r="F29"/>
+      <c r="A29" s="6">
+        <v>202606040803</v>
+      </c>
+      <c r="B29" s="6">
+        <v>3</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="6">
+        <v>55</v>
+      </c>
+      <c r="E29" s="6">
+        <v>67.2</v>
+      </c>
+      <c r="F29" s="6">
+        <v>53</v>
+      </c>
       <c r="G29"/>
       <c r="H29"/>
       <c r="I29"/>
@@ -2291,12 +2375,24 @@
       <c r="O29"/>
     </row>
     <row r="30" spans="1:15">
-      <c r="A30"/>
-      <c r="B30"/>
-      <c r="C30"/>
-      <c r="D30"/>
-      <c r="E30"/>
-      <c r="F30"/>
+      <c r="A30" s="6">
+        <v>202606040803</v>
+      </c>
+      <c r="B30" s="6">
+        <v>4</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="6">
+        <v>55</v>
+      </c>
+      <c r="E30" s="6">
+        <v>12.2</v>
+      </c>
+      <c r="F30" s="6">
+        <v>13</v>
+      </c>
       <c r="G30"/>
       <c r="H30"/>
       <c r="I30"/>
@@ -2308,29 +2404,55 @@
       <c r="O30"/>
     </row>
     <row r="31" spans="1:15">
-      <c r="A31"/>
-      <c r="B31"/>
-      <c r="C31"/>
-      <c r="D31"/>
-      <c r="E31"/>
-      <c r="F31"/>
+      <c r="A31" s="6">
+        <v>202606040803</v>
+      </c>
+      <c r="B31" s="6">
+        <v>5</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="6">
+        <v>55</v>
+      </c>
+      <c r="E31" s="6">
+        <v>55</v>
+      </c>
+      <c r="F31" s="6">
+        <v>41</v>
+      </c>
       <c r="G31"/>
       <c r="H31"/>
       <c r="I31"/>
       <c r="J31"/>
-      <c r="K31"/>
+      <c r="K31" s="6">
+        <v>1</v>
+      </c>
       <c r="L31"/>
       <c r="M31"/>
       <c r="N31"/>
       <c r="O31"/>
     </row>
     <row r="32" spans="1:15">
-      <c r="A32"/>
-      <c r="B32"/>
-      <c r="C32"/>
-      <c r="D32"/>
-      <c r="E32"/>
-      <c r="F32"/>
+      <c r="A32" s="6">
+        <v>202606040803</v>
+      </c>
+      <c r="B32" s="6">
+        <v>6</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="6">
+        <v>55</v>
+      </c>
+      <c r="E32" s="6">
+        <v>4.3</v>
+      </c>
+      <c r="F32" s="6">
+        <v>6</v>
+      </c>
       <c r="G32"/>
       <c r="H32"/>
       <c r="I32"/>
@@ -2341,44 +2463,89 @@
       <c r="N32"/>
       <c r="O32"/>
     </row>
-    <row r="33" spans="2:15">
-      <c r="B33"/>
-      <c r="C33"/>
-      <c r="D33"/>
-      <c r="E33"/>
-      <c r="F33"/>
+    <row r="33" spans="1:15">
+      <c r="A33" s="6">
+        <v>202606040803</v>
+      </c>
+      <c r="B33" s="6">
+        <v>7</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" s="6">
+        <v>55</v>
+      </c>
+      <c r="E33" s="6">
+        <v>8.8</v>
+      </c>
+      <c r="F33" s="6">
+        <v>12</v>
+      </c>
       <c r="G33"/>
       <c r="H33"/>
       <c r="I33"/>
       <c r="J33"/>
-      <c r="K33"/>
+      <c r="K33" s="6">
+        <v>1</v>
+      </c>
       <c r="L33"/>
-      <c r="M33"/>
+      <c r="M33" s="6">
+        <v>1</v>
+      </c>
       <c r="N33"/>
       <c r="O33"/>
     </row>
-    <row r="34" spans="2:15">
-      <c r="B34"/>
-      <c r="C34"/>
-      <c r="D34"/>
-      <c r="E34"/>
-      <c r="F34"/>
+    <row r="34" spans="1:15">
+      <c r="A34" s="6">
+        <v>202606040803</v>
+      </c>
+      <c r="B34" s="6">
+        <v>8</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D34" s="6">
+        <v>55</v>
+      </c>
+      <c r="E34" s="6">
+        <v>7.6</v>
+      </c>
+      <c r="F34" s="6">
+        <v>12</v>
+      </c>
       <c r="G34"/>
       <c r="H34"/>
       <c r="I34"/>
       <c r="J34"/>
-      <c r="K34"/>
+      <c r="K34" s="6">
+        <v>1</v>
+      </c>
       <c r="L34"/>
       <c r="M34"/>
       <c r="N34"/>
       <c r="O34"/>
     </row>
-    <row r="35" spans="2:15">
-      <c r="B35"/>
-      <c r="C35"/>
-      <c r="D35"/>
-      <c r="E35"/>
-      <c r="F35"/>
+    <row r="35" spans="1:15">
+      <c r="A35" s="6">
+        <v>202606040803</v>
+      </c>
+      <c r="B35" s="6">
+        <v>9</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" s="6">
+        <v>55</v>
+      </c>
+      <c r="E35" s="6">
+        <v>34.2</v>
+      </c>
+      <c r="F35" s="6">
+        <v>30</v>
+      </c>
       <c r="G35"/>
       <c r="H35"/>
       <c r="I35"/>
@@ -2389,6 +2556,247 @@
       <c r="N35"/>
       <c r="O35"/>
     </row>
+    <row r="36" spans="1:15">
+      <c r="A36" s="6">
+        <v>202606040803</v>
+      </c>
+      <c r="B36" s="6">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D36" s="6">
+        <v>55</v>
+      </c>
+      <c r="E36" s="6">
+        <v>5.7</v>
+      </c>
+      <c r="F36" s="6">
+        <v>10</v>
+      </c>
+      <c r="G36"/>
+      <c r="H36"/>
+      <c r="I36"/>
+      <c r="J36"/>
+      <c r="K36"/>
+      <c r="L36"/>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36"/>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" s="6">
+        <v>202606040803</v>
+      </c>
+      <c r="B37" s="6">
+        <v>11</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D37" s="6">
+        <v>55</v>
+      </c>
+      <c r="E37" s="6">
+        <v>5.6</v>
+      </c>
+      <c r="F37" s="6">
+        <v>10</v>
+      </c>
+      <c r="G37"/>
+      <c r="H37"/>
+      <c r="I37"/>
+      <c r="J37"/>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" s="6">
+        <v>202606040803</v>
+      </c>
+      <c r="B38" s="6">
+        <v>12</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D38" s="6">
+        <v>55</v>
+      </c>
+      <c r="E38" s="6">
+        <v>8.4</v>
+      </c>
+      <c r="F38" s="6">
+        <v>11</v>
+      </c>
+      <c r="G38"/>
+      <c r="H38"/>
+      <c r="I38"/>
+      <c r="J38"/>
+      <c r="K38"/>
+      <c r="L38"/>
+      <c r="M38"/>
+      <c r="N38"/>
+      <c r="O38"/>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" s="6">
+        <v>202606040803</v>
+      </c>
+      <c r="B39" s="6">
+        <v>13</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39" s="6">
+        <v>55</v>
+      </c>
+      <c r="E39" s="6">
+        <v>24.3</v>
+      </c>
+      <c r="F39" s="6">
+        <v>26</v>
+      </c>
+      <c r="G39"/>
+      <c r="H39"/>
+      <c r="I39"/>
+      <c r="J39"/>
+      <c r="K39"/>
+      <c r="L39"/>
+      <c r="M39" s="6">
+        <v>1</v>
+      </c>
+      <c r="N39"/>
+      <c r="O39"/>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" s="6">
+        <v>202606040803</v>
+      </c>
+      <c r="B40" s="6">
+        <v>14</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D40" s="6">
+        <v>55</v>
+      </c>
+      <c r="E40" s="6">
+        <v>12.2</v>
+      </c>
+      <c r="F40" s="6">
+        <v>15</v>
+      </c>
+      <c r="G40"/>
+      <c r="H40"/>
+      <c r="I40"/>
+      <c r="J40"/>
+      <c r="K40"/>
+      <c r="L40"/>
+      <c r="M40" s="6">
+        <v>1</v>
+      </c>
+      <c r="N40"/>
+      <c r="O40"/>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" s="6">
+        <v>202606040803</v>
+      </c>
+      <c r="B41" s="6">
+        <v>15</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D41" s="6">
+        <v>55</v>
+      </c>
+      <c r="E41" s="6">
+        <v>19.9</v>
+      </c>
+      <c r="F41" s="6">
+        <v>20</v>
+      </c>
+      <c r="G41"/>
+      <c r="H41"/>
+      <c r="I41"/>
+      <c r="J41"/>
+      <c r="K41"/>
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+    </row>
+    <row r="42" spans="1:15">
+      <c r="A42" s="6">
+        <v>202606040803</v>
+      </c>
+      <c r="B42" s="6">
+        <v>16</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D42" s="6">
+        <v>55</v>
+      </c>
+      <c r="E42" s="6">
+        <v>24.1</v>
+      </c>
+      <c r="F42" s="6">
+        <v>19</v>
+      </c>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43"/>
+      <c r="B43"/>
+      <c r="C43"/>
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="F43"/>
+      <c r="G43"/>
+      <c r="H43"/>
+      <c r="I43"/>
+      <c r="J43"/>
+      <c r="K43"/>
+      <c r="L43"/>
+      <c r="M43"/>
+      <c r="N43"/>
+      <c r="O43"/>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44"/>
+      <c r="B44"/>
+      <c r="C44"/>
+      <c r="D44"/>
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="H44"/>
+      <c r="I44"/>
+      <c r="J44"/>
+      <c r="K44"/>
+      <c r="L44"/>
+      <c r="M44"/>
+      <c r="N44"/>
+      <c r="O44"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/today_race2.xlsx
+++ b/today_race2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
   <si>
     <t>レースID</t>
   </si>
@@ -182,6 +182,492 @@
   </si>
   <si>
     <t>ココル</t>
+  </si>
+  <si>
+    <t>プラチナトレジャー</t>
+  </si>
+  <si>
+    <t>メイショウソムリエ</t>
+  </si>
+  <si>
+    <t>ネビーイーム</t>
+  </si>
+  <si>
+    <t>トゥラッタッタ</t>
+  </si>
+  <si>
+    <t>コレクテイニア</t>
+  </si>
+  <si>
+    <t>アクロスザリバー</t>
+  </si>
+  <si>
+    <t>レックスダミアーニ</t>
+  </si>
+  <si>
+    <t>エバーラスティング</t>
+  </si>
+  <si>
+    <t>ヴァイスリッター</t>
+  </si>
+  <si>
+    <t>フェイマスジャズ</t>
+  </si>
+  <si>
+    <t>ニシノカチオトコ</t>
+  </si>
+  <si>
+    <t>ブンブクチャガマ</t>
+  </si>
+  <si>
+    <t>スペーストラベラー</t>
+  </si>
+  <si>
+    <t>ブーケフォーミー</t>
+  </si>
+  <si>
+    <t>ハナミヤビ</t>
+  </si>
+  <si>
+    <t>ペプチドデバイス</t>
+  </si>
+  <si>
+    <t>ゾネンバーデン</t>
+  </si>
+  <si>
+    <t>ジャロロッソ</t>
+  </si>
+  <si>
+    <t>サヴィッジブロウ</t>
+  </si>
+  <si>
+    <t>シダモフレイバー</t>
+  </si>
+  <si>
+    <t>ミアルーチェ</t>
+  </si>
+  <si>
+    <t>ストーリーオブラブ</t>
+  </si>
+  <si>
+    <t>ノーブルクラウド</t>
+  </si>
+  <si>
+    <t>サラサチャチャチャ</t>
+  </si>
+  <si>
+    <t>キューティリップ</t>
+  </si>
+  <si>
+    <t>ベルフィーヌ</t>
+  </si>
+  <si>
+    <t>リュミナーズ</t>
+  </si>
+  <si>
+    <t>マイバラード</t>
+  </si>
+  <si>
+    <t>マイネルクオリア</t>
+  </si>
+  <si>
+    <t>サクラアドリア</t>
+  </si>
+  <si>
+    <t>ジンガー</t>
+  </si>
+  <si>
+    <t>ベルウッドバイオ</t>
+  </si>
+  <si>
+    <t>ダノンファンスター</t>
+  </si>
+  <si>
+    <t>グランアルト</t>
+  </si>
+  <si>
+    <t>リアルショット</t>
+  </si>
+  <si>
+    <t>リーゼノアール</t>
+  </si>
+  <si>
+    <t>ペプチドドリーム</t>
+  </si>
+  <si>
+    <t>ロスパレドネス</t>
+  </si>
+  <si>
+    <t>ルンベーラ</t>
+  </si>
+  <si>
+    <t>カテドラルクォーツ</t>
+  </si>
+  <si>
+    <t>タイキアロハ</t>
+  </si>
+  <si>
+    <t>ハードワーカー</t>
+  </si>
+  <si>
+    <t>ミッドセンチュリー</t>
+  </si>
+  <si>
+    <t>ヴァルカンテソーロ</t>
+  </si>
+  <si>
+    <t>キングプロフィット</t>
+  </si>
+  <si>
+    <t>コウジハラ</t>
+  </si>
+  <si>
+    <t>ビアフォーナウ</t>
+  </si>
+  <si>
+    <t>ステラノヴァ</t>
+  </si>
+  <si>
+    <t>ラルフテソーロ</t>
+  </si>
+  <si>
+    <t>ヘイルメリーラン</t>
+  </si>
+  <si>
+    <t>アイファーファイト</t>
+  </si>
+  <si>
+    <t>トモジャシーマ</t>
+  </si>
+  <si>
+    <t>ヒナノムサシ</t>
+  </si>
+  <si>
+    <t>マイネルブリオン</t>
+  </si>
+  <si>
+    <t>ノアスペシャル</t>
+  </si>
+  <si>
+    <t>リゾートライン</t>
+  </si>
+  <si>
+    <t>ソニックブレイカー</t>
+  </si>
+  <si>
+    <t>ミラビリオン</t>
+  </si>
+  <si>
+    <t>スマートブル</t>
+  </si>
+  <si>
+    <t>ガールネクストドア</t>
+  </si>
+  <si>
+    <t>カツノテンス</t>
+  </si>
+  <si>
+    <t>ニシノリリックス</t>
+  </si>
+  <si>
+    <t>ジョドレルバンク</t>
+  </si>
+  <si>
+    <t>エイシンウルトラン</t>
+  </si>
+  <si>
+    <t>コスモプルー</t>
+  </si>
+  <si>
+    <t>タイヴァス</t>
+  </si>
+  <si>
+    <t>レオンティウス</t>
+  </si>
+  <si>
+    <t>モーモーゼロ</t>
+  </si>
+  <si>
+    <t>スタースポット</t>
+  </si>
+  <si>
+    <t>デンプシー</t>
+  </si>
+  <si>
+    <t>イゾラフェリーチェ</t>
+  </si>
+  <si>
+    <t>ウィングブルー</t>
+  </si>
+  <si>
+    <t>ジョヴィアン</t>
+  </si>
+  <si>
+    <t>ヴィヴァクラウン</t>
+  </si>
+  <si>
+    <t>トラスコンガーデン</t>
+  </si>
+  <si>
+    <t>ドリーミングアップ</t>
+  </si>
+  <si>
+    <t>レオアジャイル</t>
+  </si>
+  <si>
+    <t>ビッグフラワー</t>
+  </si>
+  <si>
+    <t>セレッソデアモール</t>
+  </si>
+  <si>
+    <t>ビービーエフォート</t>
+  </si>
+  <si>
+    <t>アイムインディ</t>
+  </si>
+  <si>
+    <t>レザンノワール</t>
+  </si>
+  <si>
+    <t>スミッコディスコ</t>
+  </si>
+  <si>
+    <t>メローネ</t>
+  </si>
+  <si>
+    <t>ピコアーガイル</t>
+  </si>
+  <si>
+    <t>エフォートレス</t>
+  </si>
+  <si>
+    <t>サウンドムーブ</t>
+  </si>
+  <si>
+    <t>ソルトブリーズ</t>
+  </si>
+  <si>
+    <t>フォルラニーニ</t>
+  </si>
+  <si>
+    <t>グラニット</t>
+  </si>
+  <si>
+    <t>アルトゥーム</t>
+  </si>
+  <si>
+    <t>エスコバル</t>
+  </si>
+  <si>
+    <t>インパクトシー</t>
+  </si>
+  <si>
+    <t>ナヴォーナ</t>
+  </si>
+  <si>
+    <t>ウォータークラーク</t>
+  </si>
+  <si>
+    <t>マイネルフルムーン</t>
+  </si>
+  <si>
+    <t>マテンロウブラボー</t>
+  </si>
+  <si>
+    <t>セブンマジシャン</t>
+  </si>
+  <si>
+    <t>テンミラクルスター</t>
+  </si>
+  <si>
+    <t>ライヴレッドアイ</t>
+  </si>
+  <si>
+    <t>ホーリーブライト</t>
+  </si>
+  <si>
+    <t>キボウノホシ</t>
+  </si>
+  <si>
+    <t>グラスブランシュ</t>
+  </si>
+  <si>
+    <t>ロッカバイベイビー</t>
+  </si>
+  <si>
+    <t>モーゲンセン</t>
+  </si>
+  <si>
+    <t>トヨサカエ</t>
+  </si>
+  <si>
+    <t>マサノピンクレディ</t>
+  </si>
+  <si>
+    <t>サマースイートピー</t>
+  </si>
+  <si>
+    <t>エリカマユーリ</t>
+  </si>
+  <si>
+    <t>ルーフオブヘヴン</t>
+  </si>
+  <si>
+    <t>ホウオウプレミア</t>
+  </si>
+  <si>
+    <t>クインズポラリス</t>
+  </si>
+  <si>
+    <t>ショウナンタハティ</t>
+  </si>
+  <si>
+    <t>バシレイア</t>
+  </si>
+  <si>
+    <t>ホウオウフロイト</t>
+  </si>
+  <si>
+    <t>テンハッピー</t>
+  </si>
+  <si>
+    <t>ギブリ</t>
+  </si>
+  <si>
+    <t>ルージュラボルタ</t>
+  </si>
+  <si>
+    <t>ゴウオン</t>
+  </si>
+  <si>
+    <t>カフジカニステル</t>
+  </si>
+  <si>
+    <t>ブラスバンド</t>
+  </si>
+  <si>
+    <t>レクリドジョワ</t>
+  </si>
+  <si>
+    <t>ウォーターケプリ</t>
+  </si>
+  <si>
+    <t>ポエジア</t>
+  </si>
+  <si>
+    <t>フライウィズユー</t>
+  </si>
+  <si>
+    <t>ロックウイズミー</t>
+  </si>
+  <si>
+    <t>モンサンラパージュ</t>
+  </si>
+  <si>
+    <t>ヒノトリ</t>
+  </si>
+  <si>
+    <t>フィオッコローザ</t>
+  </si>
+  <si>
+    <t>ランゲ</t>
+  </si>
+  <si>
+    <t>ランドブレイブ</t>
+  </si>
+  <si>
+    <t>ケイアイアマゾン</t>
+  </si>
+  <si>
+    <t>ビズロード</t>
+  </si>
+  <si>
+    <t>エイシンマールス</t>
+  </si>
+  <si>
+    <t>シーリュウシー</t>
+  </si>
+  <si>
+    <t>サンマルミッション</t>
+  </si>
+  <si>
+    <t>ブルーストレイル</t>
+  </si>
+  <si>
+    <t>ウルフ</t>
+  </si>
+  <si>
+    <t>モズプリヴェール</t>
+  </si>
+  <si>
+    <t>メイショウペイト</t>
+  </si>
+  <si>
+    <t>ブリオメンテ</t>
+  </si>
+  <si>
+    <t>ワルトシュタイン</t>
+  </si>
+  <si>
+    <t>ミランド</t>
+  </si>
+  <si>
+    <t>ダノンアンドレ</t>
+  </si>
+  <si>
+    <t>ララオウ</t>
+  </si>
+  <si>
+    <t>シオンダンサー</t>
+  </si>
+  <si>
+    <t>ジューンアヲニヨシ</t>
+  </si>
+  <si>
+    <t>ゼットリアン</t>
+  </si>
+  <si>
+    <t>メイショウズイウン</t>
+  </si>
+  <si>
+    <t>ダイシンピスケス</t>
+  </si>
+  <si>
+    <t>ハピ</t>
+  </si>
+  <si>
+    <t>ギュルヴィ</t>
+  </si>
+  <si>
+    <t>ミッキークレスト</t>
+  </si>
+  <si>
+    <t>ダブルジョーク</t>
+  </si>
+  <si>
+    <t>ルシュヴァルドール</t>
+  </si>
+  <si>
+    <t>サイモンザナドゥ</t>
+  </si>
+  <si>
+    <t>ヴァルツァーシャル</t>
+  </si>
+  <si>
+    <t>マイノワール</t>
+  </si>
+  <si>
+    <t>ラムジェット</t>
+  </si>
+  <si>
+    <t>リアレスト</t>
+  </si>
+  <si>
+    <t>カズタンジャー</t>
+  </si>
+  <si>
+    <t>オニャンコポン</t>
   </si>
 </sst>
 </file>
@@ -1187,7 +1673,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:Q206"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="17.5555555555556" style="1" customWidth="1"/>
@@ -2764,38 +3250,6390 @@
       <c r="O42"/>
     </row>
     <row r="43" spans="1:15">
-      <c r="A43"/>
-      <c r="B43"/>
-      <c r="C43"/>
-      <c r="D43"/>
-      <c r="E43"/>
-      <c r="F43"/>
+      <c r="A43" s="6">
+        <v>202606040804</v>
+      </c>
+      <c r="B43" s="6">
+        <v>1</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" s="6">
+        <v>60</v>
+      </c>
+      <c r="E43" s="6">
+        <v>37</v>
+      </c>
+      <c r="F43" s="6">
+        <v>31</v>
+      </c>
       <c r="G43"/>
       <c r="H43"/>
       <c r="I43"/>
       <c r="J43"/>
-      <c r="K43"/>
+      <c r="K43" s="6">
+        <v>1</v>
+      </c>
       <c r="L43"/>
       <c r="M43"/>
       <c r="N43"/>
       <c r="O43"/>
     </row>
     <row r="44" spans="1:15">
-      <c r="A44"/>
-      <c r="B44"/>
-      <c r="C44"/>
-      <c r="D44"/>
-      <c r="E44"/>
-      <c r="F44"/>
+      <c r="A44" s="6">
+        <v>202606040804</v>
+      </c>
+      <c r="B44" s="6">
+        <v>2</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D44" s="6">
+        <v>60</v>
+      </c>
+      <c r="E44" s="6">
+        <v>36.4</v>
+      </c>
+      <c r="F44" s="6">
+        <v>30</v>
+      </c>
       <c r="G44"/>
       <c r="H44"/>
       <c r="I44"/>
       <c r="J44"/>
-      <c r="K44"/>
+      <c r="K44" s="6">
+        <v>1</v>
+      </c>
       <c r="L44"/>
-      <c r="M44"/>
+      <c r="M44" s="6">
+        <v>1</v>
+      </c>
       <c r="N44"/>
       <c r="O44"/>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" s="6">
+        <v>202606040804</v>
+      </c>
+      <c r="B45" s="6">
+        <v>3</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D45" s="6">
+        <v>61</v>
+      </c>
+      <c r="E45" s="6">
+        <v>55.9</v>
+      </c>
+      <c r="F45" s="6">
+        <v>33</v>
+      </c>
+      <c r="G45"/>
+      <c r="H45"/>
+      <c r="I45"/>
+      <c r="J45"/>
+      <c r="K45"/>
+      <c r="L45"/>
+      <c r="M45"/>
+      <c r="N45"/>
+      <c r="O45"/>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" s="6">
+        <v>202606040804</v>
+      </c>
+      <c r="B46" s="6">
+        <v>4</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D46" s="6">
+        <v>59</v>
+      </c>
+      <c r="E46" s="6">
+        <v>26</v>
+      </c>
+      <c r="F46" s="6">
+        <v>30</v>
+      </c>
+      <c r="G46"/>
+      <c r="H46"/>
+      <c r="I46"/>
+      <c r="J46"/>
+      <c r="K46"/>
+      <c r="L46"/>
+      <c r="M46"/>
+      <c r="N46"/>
+      <c r="O46"/>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" s="6">
+        <v>202606040804</v>
+      </c>
+      <c r="B47" s="6">
+        <v>5</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D47" s="6">
+        <v>59</v>
+      </c>
+      <c r="E47" s="6">
+        <v>39.2</v>
+      </c>
+      <c r="F47" s="6">
+        <v>34</v>
+      </c>
+      <c r="G47"/>
+      <c r="H47"/>
+      <c r="I47"/>
+      <c r="J47"/>
+      <c r="K47" s="6">
+        <v>1</v>
+      </c>
+      <c r="L47"/>
+      <c r="M47"/>
+      <c r="N47"/>
+      <c r="O47"/>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" s="6">
+        <v>202606040804</v>
+      </c>
+      <c r="B48" s="6">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D48" s="6">
+        <v>59</v>
+      </c>
+      <c r="E48" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="F48" s="6">
+        <v>4</v>
+      </c>
+      <c r="G48"/>
+      <c r="H48"/>
+      <c r="I48"/>
+      <c r="J48"/>
+      <c r="K48"/>
+      <c r="L48"/>
+      <c r="M48"/>
+      <c r="N48"/>
+      <c r="O48"/>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" s="6">
+        <v>202606040805</v>
+      </c>
+      <c r="B49" s="6">
+        <v>1</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D49" s="6">
+        <v>54</v>
+      </c>
+      <c r="E49" s="6">
+        <v>4.9</v>
+      </c>
+      <c r="F49" s="6">
+        <v>5</v>
+      </c>
+      <c r="G49"/>
+      <c r="H49"/>
+      <c r="I49"/>
+      <c r="J49"/>
+      <c r="K49"/>
+      <c r="L49"/>
+      <c r="M49"/>
+      <c r="N49"/>
+      <c r="O49"/>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" s="6">
+        <v>202606040805</v>
+      </c>
+      <c r="B50" s="6">
+        <v>2</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D50" s="6">
+        <v>53</v>
+      </c>
+      <c r="E50" s="6">
+        <v>4</v>
+      </c>
+      <c r="F50" s="6">
+        <v>8</v>
+      </c>
+      <c r="G50"/>
+      <c r="H50"/>
+      <c r="I50"/>
+      <c r="J50"/>
+      <c r="K50" s="6">
+        <v>1</v>
+      </c>
+      <c r="L50"/>
+      <c r="M50"/>
+      <c r="N50"/>
+      <c r="O50"/>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" s="6">
+        <v>202606040805</v>
+      </c>
+      <c r="B51" s="6">
+        <v>3</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D51" s="6">
+        <v>55</v>
+      </c>
+      <c r="E51" s="6">
+        <v>4.7</v>
+      </c>
+      <c r="F51" s="6">
+        <v>7</v>
+      </c>
+      <c r="G51"/>
+      <c r="H51"/>
+      <c r="I51"/>
+      <c r="J51"/>
+      <c r="K51"/>
+      <c r="L51"/>
+      <c r="M51" s="6">
+        <v>1</v>
+      </c>
+      <c r="N51"/>
+      <c r="O51"/>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" s="6">
+        <v>202606040805</v>
+      </c>
+      <c r="B52" s="6">
+        <v>4</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D52" s="6">
+        <v>55</v>
+      </c>
+      <c r="E52" s="6">
+        <v>11.6</v>
+      </c>
+      <c r="F52" s="6">
+        <v>20</v>
+      </c>
+      <c r="G52"/>
+      <c r="H52"/>
+      <c r="I52"/>
+      <c r="J52"/>
+      <c r="K52"/>
+      <c r="L52"/>
+      <c r="M52" s="6">
+        <v>1</v>
+      </c>
+      <c r="N52"/>
+      <c r="O52"/>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" s="6">
+        <v>202606040805</v>
+      </c>
+      <c r="B53" s="6">
+        <v>5</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D53" s="6">
+        <v>55</v>
+      </c>
+      <c r="E53" s="6">
+        <v>26</v>
+      </c>
+      <c r="F53" s="6">
+        <v>21</v>
+      </c>
+      <c r="G53"/>
+      <c r="H53"/>
+      <c r="I53"/>
+      <c r="J53"/>
+      <c r="K53" s="6">
+        <v>1</v>
+      </c>
+      <c r="L53"/>
+      <c r="M53" s="6">
+        <v>1</v>
+      </c>
+      <c r="N53"/>
+      <c r="O53"/>
+    </row>
+    <row r="54" spans="1:15">
+      <c r="A54" s="6">
+        <v>202606040805</v>
+      </c>
+      <c r="B54" s="6">
+        <v>6</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D54" s="6">
+        <v>55</v>
+      </c>
+      <c r="E54" s="6">
+        <v>32.8</v>
+      </c>
+      <c r="F54" s="6">
+        <v>22</v>
+      </c>
+      <c r="G54"/>
+      <c r="H54"/>
+      <c r="I54"/>
+      <c r="J54"/>
+      <c r="K54"/>
+      <c r="L54"/>
+      <c r="M54"/>
+      <c r="N54"/>
+      <c r="O54"/>
+    </row>
+    <row r="55" spans="1:15">
+      <c r="A55" s="6">
+        <v>202606040805</v>
+      </c>
+      <c r="B55" s="6">
+        <v>7</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D55" s="6">
+        <v>55</v>
+      </c>
+      <c r="E55" s="6">
+        <v>14.6</v>
+      </c>
+      <c r="F55" s="6">
+        <v>14</v>
+      </c>
+      <c r="G55"/>
+      <c r="H55"/>
+      <c r="I55"/>
+      <c r="J55"/>
+      <c r="K55"/>
+      <c r="L55"/>
+      <c r="M55"/>
+      <c r="N55"/>
+      <c r="O55"/>
+    </row>
+    <row r="56" spans="1:15">
+      <c r="A56" s="6">
+        <v>202606040805</v>
+      </c>
+      <c r="B56" s="6">
+        <v>8</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D56" s="6">
+        <v>55</v>
+      </c>
+      <c r="E56" s="6">
+        <v>18.9</v>
+      </c>
+      <c r="F56" s="6">
+        <v>17</v>
+      </c>
+      <c r="G56"/>
+      <c r="H56"/>
+      <c r="I56"/>
+      <c r="J56"/>
+      <c r="K56"/>
+      <c r="L56"/>
+      <c r="M56"/>
+      <c r="N56"/>
+      <c r="O56"/>
+    </row>
+    <row r="57" spans="1:15">
+      <c r="A57" s="6">
+        <v>202606040805</v>
+      </c>
+      <c r="B57" s="6">
+        <v>9</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D57" s="6">
+        <v>55</v>
+      </c>
+      <c r="E57" s="6">
+        <v>6.9</v>
+      </c>
+      <c r="F57" s="6">
+        <v>14</v>
+      </c>
+      <c r="G57"/>
+      <c r="H57"/>
+      <c r="I57"/>
+      <c r="J57"/>
+      <c r="K57"/>
+      <c r="L57"/>
+      <c r="M57"/>
+      <c r="N57"/>
+      <c r="O57"/>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="A58" s="6">
+        <v>202606040805</v>
+      </c>
+      <c r="B58" s="6">
+        <v>10</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D58" s="6">
+        <v>55</v>
+      </c>
+      <c r="E58" s="6">
+        <v>66.4</v>
+      </c>
+      <c r="F58" s="6">
+        <v>40</v>
+      </c>
+      <c r="G58"/>
+      <c r="H58"/>
+      <c r="I58"/>
+      <c r="J58"/>
+      <c r="K58" s="6">
+        <v>1</v>
+      </c>
+      <c r="L58"/>
+      <c r="M58" s="6">
+        <v>1</v>
+      </c>
+      <c r="N58"/>
+      <c r="O58"/>
+    </row>
+    <row r="59" spans="1:15">
+      <c r="A59" s="6">
+        <v>202606040805</v>
+      </c>
+      <c r="B59" s="6">
+        <v>11</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D59" s="6">
+        <v>55</v>
+      </c>
+      <c r="E59" s="6">
+        <v>6.3</v>
+      </c>
+      <c r="F59" s="6">
+        <v>12</v>
+      </c>
+      <c r="G59"/>
+      <c r="H59"/>
+      <c r="I59"/>
+      <c r="J59"/>
+      <c r="K59"/>
+      <c r="L59"/>
+      <c r="M59"/>
+      <c r="N59"/>
+      <c r="O59"/>
+    </row>
+    <row r="60" spans="1:15">
+      <c r="A60" s="6">
+        <v>202606040805</v>
+      </c>
+      <c r="B60" s="6">
+        <v>12</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D60" s="6">
+        <v>55</v>
+      </c>
+      <c r="E60" s="6">
+        <v>65.6</v>
+      </c>
+      <c r="F60" s="6">
+        <v>40</v>
+      </c>
+      <c r="G60"/>
+      <c r="H60"/>
+      <c r="I60"/>
+      <c r="J60"/>
+      <c r="K60"/>
+      <c r="L60"/>
+      <c r="M60" s="6">
+        <v>1</v>
+      </c>
+      <c r="N60"/>
+      <c r="O60"/>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" s="6">
+        <v>202606040805</v>
+      </c>
+      <c r="B61" s="6">
+        <v>13</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D61" s="6">
+        <v>55</v>
+      </c>
+      <c r="E61" s="6">
+        <v>7.6</v>
+      </c>
+      <c r="F61" s="6">
+        <v>12</v>
+      </c>
+      <c r="G61"/>
+      <c r="H61"/>
+      <c r="I61"/>
+      <c r="J61"/>
+      <c r="K61"/>
+      <c r="L61"/>
+      <c r="M61"/>
+      <c r="N61"/>
+      <c r="O61"/>
+    </row>
+    <row r="62" spans="1:15">
+      <c r="A62" s="6">
+        <v>202606040805</v>
+      </c>
+      <c r="B62" s="6">
+        <v>14</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D62" s="6">
+        <v>55</v>
+      </c>
+      <c r="E62" s="6">
+        <v>29.7</v>
+      </c>
+      <c r="F62" s="6">
+        <v>22</v>
+      </c>
+      <c r="G62"/>
+      <c r="H62"/>
+      <c r="I62"/>
+      <c r="J62"/>
+      <c r="K62"/>
+      <c r="L62"/>
+      <c r="M62"/>
+      <c r="N62"/>
+      <c r="O62"/>
+    </row>
+    <row r="63" spans="1:15">
+      <c r="A63" s="6">
+        <v>202606040806</v>
+      </c>
+      <c r="B63" s="6">
+        <v>1</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D63" s="6">
+        <v>51</v>
+      </c>
+      <c r="E63" s="6">
+        <v>27.9</v>
+      </c>
+      <c r="F63" s="6">
+        <v>23</v>
+      </c>
+      <c r="G63" s="7">
+        <v>69</v>
+      </c>
+      <c r="H63" s="6">
+        <v>-166</v>
+      </c>
+      <c r="I63" s="7">
+        <v>69</v>
+      </c>
+      <c r="J63" s="6">
+        <v>108</v>
+      </c>
+      <c r="K63"/>
+      <c r="L63"/>
+      <c r="M63"/>
+      <c r="N63" s="6">
+        <v>3</v>
+      </c>
+      <c r="O63" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
+      <c r="A64" s="6">
+        <v>202606040806</v>
+      </c>
+      <c r="B64" s="6">
+        <v>2</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D64" s="6">
+        <v>53</v>
+      </c>
+      <c r="E64" s="6">
+        <v>51.3</v>
+      </c>
+      <c r="F64" s="6">
+        <v>60</v>
+      </c>
+      <c r="G64" s="7">
+        <v>100</v>
+      </c>
+      <c r="H64" s="6">
+        <v>58</v>
+      </c>
+      <c r="I64" s="7">
+        <v>84</v>
+      </c>
+      <c r="J64" s="6">
+        <v>30</v>
+      </c>
+      <c r="K64"/>
+      <c r="L64"/>
+      <c r="M64" s="6">
+        <v>1</v>
+      </c>
+      <c r="N64" s="6">
+        <v>1</v>
+      </c>
+      <c r="O64" s="6">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65" s="6">
+        <v>202606040806</v>
+      </c>
+      <c r="B65" s="6">
+        <v>3</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D65" s="6">
+        <v>53</v>
+      </c>
+      <c r="E65" s="6">
+        <v>6.1</v>
+      </c>
+      <c r="F65" s="6">
+        <v>18</v>
+      </c>
+      <c r="G65" s="7">
+        <v>54</v>
+      </c>
+      <c r="H65" s="6">
+        <v>-168</v>
+      </c>
+      <c r="I65" s="7">
+        <v>54</v>
+      </c>
+      <c r="J65" s="6">
+        <v>-168</v>
+      </c>
+      <c r="K65" s="6">
+        <v>1</v>
+      </c>
+      <c r="L65"/>
+      <c r="M65"/>
+      <c r="N65" s="6">
+        <v>7</v>
+      </c>
+      <c r="O65" s="6">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
+      <c r="A66" s="6">
+        <v>202606040806</v>
+      </c>
+      <c r="B66" s="6">
+        <v>4</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D66" s="6">
+        <v>53</v>
+      </c>
+      <c r="E66" s="6">
+        <v>59.9</v>
+      </c>
+      <c r="F66" s="6">
+        <v>63</v>
+      </c>
+      <c r="G66" s="7">
+        <v>103</v>
+      </c>
+      <c r="H66" s="6">
+        <v>42</v>
+      </c>
+      <c r="I66" s="7">
+        <v>70</v>
+      </c>
+      <c r="J66" s="6">
+        <v>25</v>
+      </c>
+      <c r="K66" s="6">
+        <v>1</v>
+      </c>
+      <c r="L66"/>
+      <c r="M66" s="6">
+        <v>1</v>
+      </c>
+      <c r="N66" s="6">
+        <v>2</v>
+      </c>
+      <c r="O66" s="6">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
+      <c r="A67" s="6">
+        <v>202606040806</v>
+      </c>
+      <c r="B67" s="6">
+        <v>5</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D67" s="6">
+        <v>56</v>
+      </c>
+      <c r="E67" s="6">
+        <v>25.3</v>
+      </c>
+      <c r="F67" s="6">
+        <v>34</v>
+      </c>
+      <c r="G67"/>
+      <c r="H67"/>
+      <c r="I67"/>
+      <c r="J67"/>
+      <c r="K67"/>
+      <c r="L67"/>
+      <c r="M67"/>
+      <c r="N67" s="6">
+        <v>5</v>
+      </c>
+      <c r="O67" s="6">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
+      <c r="A68" s="6">
+        <v>202606040806</v>
+      </c>
+      <c r="B68" s="6">
+        <v>6</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D68" s="6">
+        <v>56</v>
+      </c>
+      <c r="E68" s="6">
+        <v>9.6</v>
+      </c>
+      <c r="F68" s="6">
+        <v>11</v>
+      </c>
+      <c r="G68" s="7">
+        <v>57</v>
+      </c>
+      <c r="H68" s="6">
+        <v>-129</v>
+      </c>
+      <c r="I68" s="7">
+        <v>77</v>
+      </c>
+      <c r="J68" s="6">
+        <v>-15</v>
+      </c>
+      <c r="K68"/>
+      <c r="L68"/>
+      <c r="M68"/>
+      <c r="N68" s="6">
+        <v>6</v>
+      </c>
+      <c r="O68" s="6">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
+      <c r="A69" s="6">
+        <v>202606040806</v>
+      </c>
+      <c r="B69" s="6">
+        <v>7</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D69" s="6">
+        <v>55</v>
+      </c>
+      <c r="E69" s="6">
+        <v>19.8</v>
+      </c>
+      <c r="F69" s="6">
+        <v>26</v>
+      </c>
+      <c r="G69" s="7">
+        <v>85</v>
+      </c>
+      <c r="H69" s="6">
+        <v>23</v>
+      </c>
+      <c r="I69" s="7">
+        <v>66</v>
+      </c>
+      <c r="J69" s="6">
+        <v>2</v>
+      </c>
+      <c r="K69" s="6">
+        <v>1</v>
+      </c>
+      <c r="L69"/>
+      <c r="M69"/>
+      <c r="N69" s="6">
+        <v>4</v>
+      </c>
+      <c r="O69" s="6">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
+      <c r="A70" s="6">
+        <v>202606040807</v>
+      </c>
+      <c r="B70" s="6">
+        <v>1</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D70" s="6">
+        <v>55</v>
+      </c>
+      <c r="E70" s="6">
+        <v>11.9</v>
+      </c>
+      <c r="F70" s="6">
+        <v>15</v>
+      </c>
+      <c r="G70" s="7">
+        <v>71</v>
+      </c>
+      <c r="H70" s="6">
+        <v>28</v>
+      </c>
+      <c r="I70" s="7">
+        <v>88</v>
+      </c>
+      <c r="J70" s="6">
+        <v>69</v>
+      </c>
+      <c r="K70"/>
+      <c r="L70"/>
+      <c r="M70"/>
+      <c r="N70" s="6">
+        <v>12</v>
+      </c>
+      <c r="O70" s="6">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
+      <c r="A71" s="6">
+        <v>202606040807</v>
+      </c>
+      <c r="B71" s="6">
+        <v>2</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D71" s="6">
+        <v>55</v>
+      </c>
+      <c r="E71" s="6">
+        <v>28.1</v>
+      </c>
+      <c r="F71" s="6">
+        <v>32</v>
+      </c>
+      <c r="G71" s="7">
+        <v>86</v>
+      </c>
+      <c r="H71" s="6">
+        <v>-27</v>
+      </c>
+      <c r="I71" s="7">
+        <v>65</v>
+      </c>
+      <c r="J71" s="6">
+        <v>56</v>
+      </c>
+      <c r="K71"/>
+      <c r="L71"/>
+      <c r="M71"/>
+      <c r="N71" s="6">
+        <v>10</v>
+      </c>
+      <c r="O71" s="6">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
+      <c r="A72" s="6">
+        <v>202606040807</v>
+      </c>
+      <c r="B72" s="6">
+        <v>3</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D72" s="6">
+        <v>58</v>
+      </c>
+      <c r="E72" s="6">
+        <v>12.6</v>
+      </c>
+      <c r="F72" s="6">
+        <v>20</v>
+      </c>
+      <c r="G72" s="7">
+        <v>65</v>
+      </c>
+      <c r="H72" s="6">
+        <v>25</v>
+      </c>
+      <c r="I72" s="7">
+        <v>82</v>
+      </c>
+      <c r="J72" s="6">
+        <v>30</v>
+      </c>
+      <c r="K72"/>
+      <c r="L72"/>
+      <c r="M72"/>
+      <c r="N72" s="6">
+        <v>8</v>
+      </c>
+      <c r="O72" s="6">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
+      <c r="A73" s="6">
+        <v>202606040807</v>
+      </c>
+      <c r="B73" s="6">
+        <v>4</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D73" s="6">
+        <v>58</v>
+      </c>
+      <c r="E73" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="F73" s="6">
+        <v>4</v>
+      </c>
+      <c r="G73"/>
+      <c r="H73"/>
+      <c r="I73"/>
+      <c r="J73"/>
+      <c r="K73"/>
+      <c r="L73"/>
+      <c r="M73" s="6">
+        <v>1</v>
+      </c>
+      <c r="N73" s="6">
+        <v>18</v>
+      </c>
+      <c r="O73" s="6">
+        <v>115.4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
+      <c r="A74" s="6">
+        <v>202606040807</v>
+      </c>
+      <c r="B74" s="6">
+        <v>5</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D74" s="6">
+        <v>54</v>
+      </c>
+      <c r="E74" s="6">
+        <v>13</v>
+      </c>
+      <c r="F74" s="6">
+        <v>24</v>
+      </c>
+      <c r="G74" s="7">
+        <v>59</v>
+      </c>
+      <c r="H74" s="6">
+        <v>5</v>
+      </c>
+      <c r="I74" s="7">
+        <v>75</v>
+      </c>
+      <c r="J74" s="6">
+        <v>60</v>
+      </c>
+      <c r="K74"/>
+      <c r="L74"/>
+      <c r="M74"/>
+      <c r="N74" s="6">
+        <v>7</v>
+      </c>
+      <c r="O74" s="6">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
+      <c r="A75" s="6">
+        <v>202606040807</v>
+      </c>
+      <c r="B75" s="6">
+        <v>6</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D75" s="6">
+        <v>55</v>
+      </c>
+      <c r="E75" s="6">
+        <v>64.6</v>
+      </c>
+      <c r="F75" s="6">
+        <v>57</v>
+      </c>
+      <c r="G75" s="7">
+        <v>77</v>
+      </c>
+      <c r="H75" s="6">
+        <v>42</v>
+      </c>
+      <c r="I75" s="7">
+        <v>87</v>
+      </c>
+      <c r="J75" s="6">
+        <v>61</v>
+      </c>
+      <c r="K75" s="6">
+        <v>1</v>
+      </c>
+      <c r="L75"/>
+      <c r="M75"/>
+      <c r="N75" s="6">
+        <v>1</v>
+      </c>
+      <c r="O75" s="6">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="A76" s="6">
+        <v>202606040807</v>
+      </c>
+      <c r="B76" s="6">
+        <v>7</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D76" s="6">
+        <v>55</v>
+      </c>
+      <c r="E76" s="6">
+        <v>10.7</v>
+      </c>
+      <c r="F76" s="6">
+        <v>19</v>
+      </c>
+      <c r="G76" s="7">
+        <v>91</v>
+      </c>
+      <c r="H76" s="6">
+        <v>-50</v>
+      </c>
+      <c r="I76" s="7">
+        <v>87</v>
+      </c>
+      <c r="J76"/>
+      <c r="K76"/>
+      <c r="L76"/>
+      <c r="M76"/>
+      <c r="N76" s="6">
+        <v>11</v>
+      </c>
+      <c r="O76" s="6">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77" s="6">
+        <v>202606040807</v>
+      </c>
+      <c r="B77" s="6">
+        <v>8</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D77" s="6">
+        <v>58</v>
+      </c>
+      <c r="E77" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="F77" s="6">
+        <v>1</v>
+      </c>
+      <c r="G77" s="7">
+        <v>69</v>
+      </c>
+      <c r="H77" s="6">
+        <v>-86</v>
+      </c>
+      <c r="I77" s="7">
+        <v>69</v>
+      </c>
+      <c r="J77" s="6">
+        <v>-86</v>
+      </c>
+      <c r="K77"/>
+      <c r="L77"/>
+      <c r="M77"/>
+      <c r="N77" s="6">
+        <v>16</v>
+      </c>
+      <c r="O77" s="6">
+        <v>72.4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78" s="6">
+        <v>202606040807</v>
+      </c>
+      <c r="B78" s="6">
+        <v>9</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D78" s="6">
+        <v>58</v>
+      </c>
+      <c r="E78" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="F78" s="6">
+        <v>1</v>
+      </c>
+      <c r="G78" s="7">
+        <v>77</v>
+      </c>
+      <c r="H78" s="6">
+        <v>-161</v>
+      </c>
+      <c r="I78" s="7">
+        <v>77</v>
+      </c>
+      <c r="J78" s="6">
+        <v>-161</v>
+      </c>
+      <c r="K78"/>
+      <c r="L78"/>
+      <c r="M78"/>
+      <c r="N78" s="6">
+        <v>15</v>
+      </c>
+      <c r="O78" s="6">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79" s="6">
+        <v>202606040807</v>
+      </c>
+      <c r="B79" s="6">
+        <v>10</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D79" s="6">
+        <v>55</v>
+      </c>
+      <c r="E79" s="6">
+        <v>9.3</v>
+      </c>
+      <c r="F79" s="6">
+        <v>26</v>
+      </c>
+      <c r="G79" s="7">
+        <v>72</v>
+      </c>
+      <c r="H79" s="6">
+        <v>-138</v>
+      </c>
+      <c r="I79" s="7">
+        <v>81</v>
+      </c>
+      <c r="J79" s="6">
+        <v>49</v>
+      </c>
+      <c r="K79"/>
+      <c r="L79"/>
+      <c r="M79" s="6">
+        <v>1</v>
+      </c>
+      <c r="N79" s="6">
+        <v>3</v>
+      </c>
+      <c r="O79" s="6">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="A80" s="6">
+        <v>202606040807</v>
+      </c>
+      <c r="B80" s="6">
+        <v>11</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D80" s="6">
+        <v>55</v>
+      </c>
+      <c r="E80" s="6">
+        <v>11.2</v>
+      </c>
+      <c r="F80" s="6">
+        <v>30</v>
+      </c>
+      <c r="G80" s="7">
+        <v>81</v>
+      </c>
+      <c r="H80" s="6">
+        <v>-40</v>
+      </c>
+      <c r="I80" s="7">
+        <v>68</v>
+      </c>
+      <c r="J80" s="6">
+        <v>15</v>
+      </c>
+      <c r="K80"/>
+      <c r="L80"/>
+      <c r="M80"/>
+      <c r="N80" s="6">
+        <v>5</v>
+      </c>
+      <c r="O80" s="6">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
+      <c r="A81" s="6">
+        <v>202606040807</v>
+      </c>
+      <c r="B81" s="6">
+        <v>12</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D81" s="6">
+        <v>53</v>
+      </c>
+      <c r="E81" s="6">
+        <v>18.7</v>
+      </c>
+      <c r="F81" s="6">
+        <v>28</v>
+      </c>
+      <c r="G81" s="7">
+        <v>90</v>
+      </c>
+      <c r="H81" s="6">
+        <v>56</v>
+      </c>
+      <c r="I81" s="7">
+        <v>82</v>
+      </c>
+      <c r="J81" s="6">
+        <v>-12</v>
+      </c>
+      <c r="K81"/>
+      <c r="L81"/>
+      <c r="M81" s="6">
+        <v>1</v>
+      </c>
+      <c r="N81" s="6">
+        <v>9</v>
+      </c>
+      <c r="O81" s="6">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15">
+      <c r="A82" s="6">
+        <v>202606040807</v>
+      </c>
+      <c r="B82" s="6">
+        <v>13</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D82" s="6">
+        <v>55</v>
+      </c>
+      <c r="E82" s="6">
+        <v>11.9</v>
+      </c>
+      <c r="F82" s="6">
+        <v>30</v>
+      </c>
+      <c r="G82" s="7">
+        <v>82</v>
+      </c>
+      <c r="H82" s="6">
+        <v>74</v>
+      </c>
+      <c r="I82" s="7">
+        <v>79</v>
+      </c>
+      <c r="J82" s="6">
+        <v>-15</v>
+      </c>
+      <c r="K82" s="6">
+        <v>1</v>
+      </c>
+      <c r="L82"/>
+      <c r="M82" s="6">
+        <v>1</v>
+      </c>
+      <c r="N82" s="6">
+        <v>2</v>
+      </c>
+      <c r="O82" s="6">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15">
+      <c r="A83" s="6">
+        <v>202606040807</v>
+      </c>
+      <c r="B83" s="6">
+        <v>14</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D83" s="6">
+        <v>55</v>
+      </c>
+      <c r="E83" s="6">
+        <v>8.1</v>
+      </c>
+      <c r="F83" s="6">
+        <v>20</v>
+      </c>
+      <c r="G83" s="7">
+        <v>21</v>
+      </c>
+      <c r="H83" s="6">
+        <v>47</v>
+      </c>
+      <c r="I83" s="7">
+        <v>71</v>
+      </c>
+      <c r="J83" s="6">
+        <v>39</v>
+      </c>
+      <c r="K83"/>
+      <c r="L83"/>
+      <c r="M83"/>
+      <c r="N83" s="6">
+        <v>14</v>
+      </c>
+      <c r="O83" s="6">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15">
+      <c r="A84" s="6">
+        <v>202606040807</v>
+      </c>
+      <c r="B84" s="6">
+        <v>15</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D84" s="6">
+        <v>56</v>
+      </c>
+      <c r="E84" s="6">
+        <v>4.2</v>
+      </c>
+      <c r="F84" s="6">
+        <v>10</v>
+      </c>
+      <c r="G84" s="7">
+        <v>76</v>
+      </c>
+      <c r="H84" s="6">
+        <v>-55</v>
+      </c>
+      <c r="I84" s="7">
+        <v>53</v>
+      </c>
+      <c r="J84" s="6">
+        <v>-287</v>
+      </c>
+      <c r="K84" s="6">
+        <v>1</v>
+      </c>
+      <c r="L84"/>
+      <c r="M84" s="6">
+        <v>1</v>
+      </c>
+      <c r="N84" s="6">
+        <v>13</v>
+      </c>
+      <c r="O84" s="6">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15">
+      <c r="A85" s="6">
+        <v>202606040807</v>
+      </c>
+      <c r="B85" s="6">
+        <v>16</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D85" s="6">
+        <v>58</v>
+      </c>
+      <c r="E85" s="6">
+        <v>36</v>
+      </c>
+      <c r="F85" s="6">
+        <v>28</v>
+      </c>
+      <c r="G85" s="7">
+        <v>83</v>
+      </c>
+      <c r="H85" s="6">
+        <v>88</v>
+      </c>
+      <c r="I85" s="7">
+        <v>75</v>
+      </c>
+      <c r="J85" s="6">
+        <v>19</v>
+      </c>
+      <c r="K85"/>
+      <c r="L85"/>
+      <c r="M85"/>
+      <c r="N85" s="6">
+        <v>6</v>
+      </c>
+      <c r="O85" s="6">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15">
+      <c r="A86" s="6">
+        <v>202606040807</v>
+      </c>
+      <c r="B86" s="6">
+        <v>17</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D86" s="6">
+        <v>55</v>
+      </c>
+      <c r="E86" s="6">
+        <v>45.8</v>
+      </c>
+      <c r="F86" s="6">
+        <v>38</v>
+      </c>
+      <c r="G86" s="7">
+        <v>80</v>
+      </c>
+      <c r="H86" s="6">
+        <v>-139</v>
+      </c>
+      <c r="I86" s="7">
+        <v>81</v>
+      </c>
+      <c r="J86" s="6">
+        <v>34</v>
+      </c>
+      <c r="K86"/>
+      <c r="L86"/>
+      <c r="M86"/>
+      <c r="N86" s="6">
+        <v>4</v>
+      </c>
+      <c r="O86" s="6">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15">
+      <c r="A87" s="6">
+        <v>202606040807</v>
+      </c>
+      <c r="B87" s="6">
+        <v>18</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D87" s="6">
+        <v>56</v>
+      </c>
+      <c r="E87" s="6">
+        <v>4</v>
+      </c>
+      <c r="F87" s="6">
+        <v>6</v>
+      </c>
+      <c r="G87"/>
+      <c r="H87"/>
+      <c r="I87"/>
+      <c r="J87"/>
+      <c r="K87"/>
+      <c r="L87"/>
+      <c r="M87"/>
+      <c r="N87" s="6">
+        <v>17</v>
+      </c>
+      <c r="O87" s="6">
+        <v>73.9</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15">
+      <c r="A88" s="6">
+        <v>202606040808</v>
+      </c>
+      <c r="B88" s="6">
+        <v>1</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D88" s="6">
+        <v>54</v>
+      </c>
+      <c r="E88" s="6">
+        <v>34.9</v>
+      </c>
+      <c r="F88" s="6">
+        <v>32</v>
+      </c>
+      <c r="G88" s="7">
+        <v>103</v>
+      </c>
+      <c r="H88" s="6">
+        <v>-5</v>
+      </c>
+      <c r="I88" s="7">
+        <v>103</v>
+      </c>
+      <c r="J88" s="6">
+        <v>-5</v>
+      </c>
+      <c r="K88" s="6">
+        <v>1</v>
+      </c>
+      <c r="L88"/>
+      <c r="M88" s="6">
+        <v>1</v>
+      </c>
+      <c r="N88" s="6">
+        <v>2</v>
+      </c>
+      <c r="O88" s="6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15">
+      <c r="A89" s="6">
+        <v>202606040808</v>
+      </c>
+      <c r="B89" s="6">
+        <v>2</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D89" s="6">
+        <v>54</v>
+      </c>
+      <c r="E89" s="6">
+        <v>5.4</v>
+      </c>
+      <c r="F89" s="6">
+        <v>3</v>
+      </c>
+      <c r="G89" s="7">
+        <v>82</v>
+      </c>
+      <c r="H89" s="6">
+        <v>33</v>
+      </c>
+      <c r="I89" s="7">
+        <v>69</v>
+      </c>
+      <c r="J89" s="6">
+        <v>3</v>
+      </c>
+      <c r="K89"/>
+      <c r="L89"/>
+      <c r="M89"/>
+      <c r="N89" s="6">
+        <v>4</v>
+      </c>
+      <c r="O89" s="6">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15">
+      <c r="A90" s="6">
+        <v>202606040808</v>
+      </c>
+      <c r="B90" s="6">
+        <v>3</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D90" s="6">
+        <v>58</v>
+      </c>
+      <c r="E90" s="6">
+        <v>17.8</v>
+      </c>
+      <c r="F90" s="6">
+        <v>29</v>
+      </c>
+      <c r="G90" s="7">
+        <v>85</v>
+      </c>
+      <c r="H90" s="6">
+        <v>55</v>
+      </c>
+      <c r="I90" s="7">
+        <v>79</v>
+      </c>
+      <c r="J90" s="6">
+        <v>46</v>
+      </c>
+      <c r="K90"/>
+      <c r="L90"/>
+      <c r="M90"/>
+      <c r="N90" s="6">
+        <v>7</v>
+      </c>
+      <c r="O90" s="6">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15">
+      <c r="A91" s="6">
+        <v>202606040808</v>
+      </c>
+      <c r="B91" s="6">
+        <v>4</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D91" s="6">
+        <v>58</v>
+      </c>
+      <c r="E91" s="6">
+        <v>42.2</v>
+      </c>
+      <c r="F91" s="6">
+        <v>44</v>
+      </c>
+      <c r="G91" s="7">
+        <v>86</v>
+      </c>
+      <c r="H91" s="6">
+        <v>19</v>
+      </c>
+      <c r="I91" s="7">
+        <v>72</v>
+      </c>
+      <c r="J91" s="6">
+        <v>-95</v>
+      </c>
+      <c r="K91" s="6">
+        <v>1</v>
+      </c>
+      <c r="L91"/>
+      <c r="M91" s="6">
+        <v>1</v>
+      </c>
+      <c r="N91" s="6">
+        <v>8</v>
+      </c>
+      <c r="O91" s="6">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15">
+      <c r="A92" s="6">
+        <v>202606040808</v>
+      </c>
+      <c r="B92" s="6">
+        <v>5</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D92" s="6">
+        <v>56</v>
+      </c>
+      <c r="E92" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="F92" s="6">
+        <v>4</v>
+      </c>
+      <c r="G92" s="7">
+        <v>24</v>
+      </c>
+      <c r="H92" s="6">
+        <v>-237</v>
+      </c>
+      <c r="I92" s="7">
+        <v>35</v>
+      </c>
+      <c r="J92" s="6">
+        <v>-3</v>
+      </c>
+      <c r="K92"/>
+      <c r="L92"/>
+      <c r="M92"/>
+      <c r="N92" s="6">
+        <v>14</v>
+      </c>
+      <c r="O92" s="6">
+        <v>71.9</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15">
+      <c r="A93" s="6">
+        <v>202606040808</v>
+      </c>
+      <c r="B93" s="6">
+        <v>6</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D93" s="6">
+        <v>58</v>
+      </c>
+      <c r="E93" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="F93" s="6">
+        <v>4</v>
+      </c>
+      <c r="G93" s="7">
+        <v>58</v>
+      </c>
+      <c r="H93" s="6">
+        <v>-192</v>
+      </c>
+      <c r="I93" s="7">
+        <v>50</v>
+      </c>
+      <c r="J93" s="6">
+        <v>-130</v>
+      </c>
+      <c r="K93"/>
+      <c r="L93"/>
+      <c r="M93"/>
+      <c r="N93" s="6">
+        <v>15</v>
+      </c>
+      <c r="O93" s="6">
+        <v>75.2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15">
+      <c r="A94" s="6">
+        <v>202606040808</v>
+      </c>
+      <c r="B94" s="6">
+        <v>7</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D94" s="6">
+        <v>58</v>
+      </c>
+      <c r="E94" s="6">
+        <v>33.4</v>
+      </c>
+      <c r="F94" s="6">
+        <v>28</v>
+      </c>
+      <c r="G94" s="7">
+        <v>89</v>
+      </c>
+      <c r="H94" s="6">
+        <v>42</v>
+      </c>
+      <c r="I94" s="7">
+        <v>69</v>
+      </c>
+      <c r="J94" s="6">
+        <v>32</v>
+      </c>
+      <c r="K94"/>
+      <c r="L94"/>
+      <c r="M94"/>
+      <c r="N94" s="6">
+        <v>5</v>
+      </c>
+      <c r="O94" s="6">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15">
+      <c r="A95" s="6">
+        <v>202606040808</v>
+      </c>
+      <c r="B95" s="6">
+        <v>8</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D95" s="6">
+        <v>53</v>
+      </c>
+      <c r="E95" s="6">
+        <v>4.3</v>
+      </c>
+      <c r="F95" s="6">
+        <v>14</v>
+      </c>
+      <c r="G95" s="7">
+        <v>63</v>
+      </c>
+      <c r="H95" s="6">
+        <v>-42</v>
+      </c>
+      <c r="I95" s="7">
+        <v>70</v>
+      </c>
+      <c r="J95" s="6">
+        <v>-186</v>
+      </c>
+      <c r="K95"/>
+      <c r="L95"/>
+      <c r="M95" s="6">
+        <v>1</v>
+      </c>
+      <c r="N95" s="6">
+        <v>10</v>
+      </c>
+      <c r="O95" s="6">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15">
+      <c r="A96" s="6">
+        <v>202606040808</v>
+      </c>
+      <c r="B96" s="6">
+        <v>9</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D96" s="6">
+        <v>58</v>
+      </c>
+      <c r="E96" s="6">
+        <v>8.5</v>
+      </c>
+      <c r="F96" s="6">
+        <v>12</v>
+      </c>
+      <c r="G96" s="7">
+        <v>82</v>
+      </c>
+      <c r="H96" s="6">
+        <v>-15</v>
+      </c>
+      <c r="I96" s="7">
+        <v>73</v>
+      </c>
+      <c r="J96" s="6">
+        <v>-5</v>
+      </c>
+      <c r="K96"/>
+      <c r="L96"/>
+      <c r="M96"/>
+      <c r="N96" s="6">
+        <v>12</v>
+      </c>
+      <c r="O96" s="6">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15">
+      <c r="A97" s="6">
+        <v>202606040808</v>
+      </c>
+      <c r="B97" s="6">
+        <v>10</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D97" s="6">
+        <v>56</v>
+      </c>
+      <c r="E97" s="6">
+        <v>27.3</v>
+      </c>
+      <c r="F97" s="6">
+        <v>20</v>
+      </c>
+      <c r="G97" s="7">
+        <v>70</v>
+      </c>
+      <c r="H97" s="6">
+        <v>6</v>
+      </c>
+      <c r="I97" s="7">
+        <v>94</v>
+      </c>
+      <c r="J97" s="6">
+        <v>106</v>
+      </c>
+      <c r="K97"/>
+      <c r="L97"/>
+      <c r="M97"/>
+      <c r="N97" s="6">
+        <v>9</v>
+      </c>
+      <c r="O97" s="6">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15">
+      <c r="A98" s="6">
+        <v>202606040808</v>
+      </c>
+      <c r="B98" s="6">
+        <v>11</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D98" s="6">
+        <v>56</v>
+      </c>
+      <c r="E98" s="6">
+        <v>13.9</v>
+      </c>
+      <c r="F98" s="6">
+        <v>24</v>
+      </c>
+      <c r="G98" s="7">
+        <v>65</v>
+      </c>
+      <c r="H98" s="6">
+        <v>-125</v>
+      </c>
+      <c r="I98" s="7">
+        <v>86</v>
+      </c>
+      <c r="J98" s="6">
+        <v>41</v>
+      </c>
+      <c r="K98"/>
+      <c r="L98"/>
+      <c r="M98" s="6">
+        <v>1</v>
+      </c>
+      <c r="N98" s="6">
+        <v>3</v>
+      </c>
+      <c r="O98" s="6">
+        <v>8.8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15">
+      <c r="A99" s="6">
+        <v>202606040808</v>
+      </c>
+      <c r="B99" s="6">
+        <v>12</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D99" s="6">
+        <v>56</v>
+      </c>
+      <c r="E99" s="6">
+        <v>63.6</v>
+      </c>
+      <c r="F99" s="6">
+        <v>60</v>
+      </c>
+      <c r="G99" s="7">
+        <v>77</v>
+      </c>
+      <c r="H99" s="6">
+        <v>29</v>
+      </c>
+      <c r="I99" s="7">
+        <v>85</v>
+      </c>
+      <c r="J99" s="6">
+        <v>63</v>
+      </c>
+      <c r="K99" s="6">
+        <v>1</v>
+      </c>
+      <c r="L99"/>
+      <c r="M99"/>
+      <c r="N99" s="6">
+        <v>1</v>
+      </c>
+      <c r="O99" s="6">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15">
+      <c r="A100" s="6">
+        <v>202606040808</v>
+      </c>
+      <c r="B100" s="6">
+        <v>13</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D100" s="6">
+        <v>56</v>
+      </c>
+      <c r="E100" s="6">
+        <v>24.7</v>
+      </c>
+      <c r="F100" s="6">
+        <v>25</v>
+      </c>
+      <c r="G100" s="7">
+        <v>60</v>
+      </c>
+      <c r="H100" s="6">
+        <v>94</v>
+      </c>
+      <c r="I100" s="7">
+        <v>74</v>
+      </c>
+      <c r="J100" s="6">
+        <v>101</v>
+      </c>
+      <c r="K100"/>
+      <c r="L100"/>
+      <c r="M100"/>
+      <c r="N100" s="6">
+        <v>6</v>
+      </c>
+      <c r="O100" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15">
+      <c r="A101" s="6">
+        <v>202606040808</v>
+      </c>
+      <c r="B101" s="6">
+        <v>14</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D101" s="6">
+        <v>56</v>
+      </c>
+      <c r="E101" s="6">
+        <v>6.3</v>
+      </c>
+      <c r="F101" s="6">
+        <v>5</v>
+      </c>
+      <c r="G101" s="7">
+        <v>69</v>
+      </c>
+      <c r="H101" s="6">
+        <v>-4</v>
+      </c>
+      <c r="I101" s="7">
+        <v>64</v>
+      </c>
+      <c r="J101" s="6">
+        <v>-78</v>
+      </c>
+      <c r="K101"/>
+      <c r="L101"/>
+      <c r="M101"/>
+      <c r="N101" s="6">
+        <v>13</v>
+      </c>
+      <c r="O101" s="6">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15">
+      <c r="A102" s="6">
+        <v>202606040808</v>
+      </c>
+      <c r="B102" s="6">
+        <v>15</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D102" s="6">
+        <v>56</v>
+      </c>
+      <c r="E102" s="6">
+        <v>5.8</v>
+      </c>
+      <c r="F102" s="6">
+        <v>4</v>
+      </c>
+      <c r="G102" s="7">
+        <v>56</v>
+      </c>
+      <c r="H102" s="6">
+        <v>-99</v>
+      </c>
+      <c r="I102" s="7">
+        <v>64</v>
+      </c>
+      <c r="J102" s="6">
+        <v>-41</v>
+      </c>
+      <c r="K102"/>
+      <c r="L102"/>
+      <c r="M102"/>
+      <c r="N102" s="6">
+        <v>16</v>
+      </c>
+      <c r="O102" s="6">
+        <v>82.7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15">
+      <c r="A103" s="6">
+        <v>202606040808</v>
+      </c>
+      <c r="B103" s="6">
+        <v>16</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D103" s="6">
+        <v>55</v>
+      </c>
+      <c r="E103" s="6">
+        <v>5.1</v>
+      </c>
+      <c r="F103" s="6">
+        <v>6</v>
+      </c>
+      <c r="G103" s="7">
+        <v>58</v>
+      </c>
+      <c r="H103" s="6">
+        <v>-145</v>
+      </c>
+      <c r="I103" s="7">
+        <v>78</v>
+      </c>
+      <c r="J103" s="6">
+        <v>-4</v>
+      </c>
+      <c r="K103"/>
+      <c r="L103"/>
+      <c r="M103"/>
+      <c r="N103" s="6">
+        <v>11</v>
+      </c>
+      <c r="O103" s="6">
+        <v>35.9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15">
+      <c r="A104" s="6">
+        <v>202606040809</v>
+      </c>
+      <c r="B104" s="6">
+        <v>1</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D104" s="6">
+        <v>55</v>
+      </c>
+      <c r="E104" s="6">
+        <v>11.9</v>
+      </c>
+      <c r="F104" s="6">
+        <v>18</v>
+      </c>
+      <c r="G104" s="7">
+        <v>50</v>
+      </c>
+      <c r="H104" s="6">
+        <v>21</v>
+      </c>
+      <c r="I104" s="7">
+        <v>57</v>
+      </c>
+      <c r="J104" s="6">
+        <v>-126</v>
+      </c>
+      <c r="K104" s="6">
+        <v>1</v>
+      </c>
+      <c r="L104"/>
+      <c r="M104"/>
+      <c r="N104" s="6">
+        <v>6</v>
+      </c>
+      <c r="O104" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15">
+      <c r="A105" s="6">
+        <v>202606040809</v>
+      </c>
+      <c r="B105" s="6">
+        <v>2</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D105" s="6">
+        <v>55</v>
+      </c>
+      <c r="E105" s="6">
+        <v>77.6</v>
+      </c>
+      <c r="F105" s="6">
+        <v>48</v>
+      </c>
+      <c r="G105" s="7">
+        <v>76</v>
+      </c>
+      <c r="H105" s="6">
+        <v>78</v>
+      </c>
+      <c r="I105" s="7">
+        <v>76</v>
+      </c>
+      <c r="J105" s="6">
+        <v>78</v>
+      </c>
+      <c r="K105"/>
+      <c r="L105"/>
+      <c r="M105"/>
+      <c r="N105" s="6">
+        <v>1</v>
+      </c>
+      <c r="O105" s="6">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15">
+      <c r="A106" s="6">
+        <v>202606040809</v>
+      </c>
+      <c r="B106" s="6">
+        <v>3</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D106" s="6">
+        <v>55</v>
+      </c>
+      <c r="E106" s="6">
+        <v>26.1</v>
+      </c>
+      <c r="F106" s="6">
+        <v>21</v>
+      </c>
+      <c r="G106" s="7">
+        <v>77</v>
+      </c>
+      <c r="H106" s="6">
+        <v>53</v>
+      </c>
+      <c r="I106" s="7">
+        <v>77</v>
+      </c>
+      <c r="J106" s="6">
+        <v>53</v>
+      </c>
+      <c r="K106"/>
+      <c r="L106"/>
+      <c r="M106"/>
+      <c r="N106" s="6">
+        <v>7</v>
+      </c>
+      <c r="O106" s="6">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15">
+      <c r="A107" s="6">
+        <v>202606040809</v>
+      </c>
+      <c r="B107" s="6">
+        <v>4</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D107" s="6">
+        <v>55</v>
+      </c>
+      <c r="E107" s="6">
+        <v>37.5</v>
+      </c>
+      <c r="F107" s="6">
+        <v>28</v>
+      </c>
+      <c r="G107" s="7">
+        <v>81</v>
+      </c>
+      <c r="H107" s="6">
+        <v>68</v>
+      </c>
+      <c r="I107" s="7">
+        <v>70</v>
+      </c>
+      <c r="J107" s="6">
+        <v>36</v>
+      </c>
+      <c r="K107"/>
+      <c r="L107"/>
+      <c r="M107" s="6">
+        <v>1</v>
+      </c>
+      <c r="N107" s="6">
+        <v>4</v>
+      </c>
+      <c r="O107" s="6">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15">
+      <c r="A108" s="6">
+        <v>202606040809</v>
+      </c>
+      <c r="B108" s="6">
+        <v>5</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D108" s="6">
+        <v>55</v>
+      </c>
+      <c r="E108" s="6">
+        <v>29.1</v>
+      </c>
+      <c r="F108" s="6">
+        <v>28</v>
+      </c>
+      <c r="G108" s="7">
+        <v>10</v>
+      </c>
+      <c r="H108" s="6">
+        <v>45</v>
+      </c>
+      <c r="I108" s="7">
+        <v>10</v>
+      </c>
+      <c r="J108" s="6">
+        <v>45</v>
+      </c>
+      <c r="K108" s="6">
+        <v>1</v>
+      </c>
+      <c r="L108"/>
+      <c r="M108" s="6">
+        <v>1</v>
+      </c>
+      <c r="N108" s="6">
+        <v>5</v>
+      </c>
+      <c r="O108" s="6">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15">
+      <c r="A109" s="6">
+        <v>202606040809</v>
+      </c>
+      <c r="B109" s="6">
+        <v>6</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D109" s="6">
+        <v>55</v>
+      </c>
+      <c r="E109" s="6">
+        <v>48.4</v>
+      </c>
+      <c r="F109" s="6">
+        <v>26</v>
+      </c>
+      <c r="G109" s="7">
+        <v>85</v>
+      </c>
+      <c r="H109" s="6">
+        <v>81</v>
+      </c>
+      <c r="I109" s="7">
+        <v>74</v>
+      </c>
+      <c r="J109" s="6">
+        <v>63</v>
+      </c>
+      <c r="K109"/>
+      <c r="L109"/>
+      <c r="M109" s="6">
+        <v>1</v>
+      </c>
+      <c r="N109" s="6">
+        <v>3</v>
+      </c>
+      <c r="O109" s="6">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15">
+      <c r="A110" s="6">
+        <v>202606040809</v>
+      </c>
+      <c r="B110" s="6">
+        <v>7</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D110" s="6">
+        <v>55</v>
+      </c>
+      <c r="E110" s="6">
+        <v>6.2</v>
+      </c>
+      <c r="F110" s="6">
+        <v>2</v>
+      </c>
+      <c r="G110" s="7">
+        <v>54</v>
+      </c>
+      <c r="H110" s="6">
+        <v>-29</v>
+      </c>
+      <c r="I110" s="7">
+        <v>75</v>
+      </c>
+      <c r="J110" s="6">
+        <v>-29</v>
+      </c>
+      <c r="K110"/>
+      <c r="L110"/>
+      <c r="M110"/>
+      <c r="N110" s="6">
+        <v>8</v>
+      </c>
+      <c r="O110" s="6">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15">
+      <c r="A111" s="6">
+        <v>202606040809</v>
+      </c>
+      <c r="B111" s="6">
+        <v>8</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D111" s="6">
+        <v>55</v>
+      </c>
+      <c r="E111" s="6">
+        <v>63.3</v>
+      </c>
+      <c r="F111" s="6">
+        <v>42</v>
+      </c>
+      <c r="G111" s="7">
+        <v>70</v>
+      </c>
+      <c r="H111" s="6">
+        <v>96</v>
+      </c>
+      <c r="I111" s="7">
+        <v>70</v>
+      </c>
+      <c r="J111" s="6">
+        <v>96</v>
+      </c>
+      <c r="K111" s="6">
+        <v>1</v>
+      </c>
+      <c r="L111"/>
+      <c r="M111" s="6">
+        <v>1</v>
+      </c>
+      <c r="N111" s="6">
+        <v>2</v>
+      </c>
+      <c r="O111" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15">
+      <c r="A112" s="6">
+        <v>202606040810</v>
+      </c>
+      <c r="B112" s="6">
+        <v>1</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D112" s="6">
+        <v>56</v>
+      </c>
+      <c r="E112" s="6">
+        <v>32.5</v>
+      </c>
+      <c r="F112" s="6">
+        <v>32</v>
+      </c>
+      <c r="G112" s="7">
+        <v>86</v>
+      </c>
+      <c r="H112" s="6">
+        <v>-1</v>
+      </c>
+      <c r="I112" s="7">
+        <v>85</v>
+      </c>
+      <c r="J112" s="6">
+        <v>47</v>
+      </c>
+      <c r="K112" s="6">
+        <v>1</v>
+      </c>
+      <c r="L112"/>
+      <c r="M112" s="6">
+        <v>1</v>
+      </c>
+      <c r="N112" s="6">
+        <v>4</v>
+      </c>
+      <c r="O112" s="6">
+        <v>9.7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15">
+      <c r="A113" s="6">
+        <v>202606040810</v>
+      </c>
+      <c r="B113" s="6">
+        <v>2</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D113" s="6">
+        <v>56</v>
+      </c>
+      <c r="E113" s="6">
+        <v>50.4</v>
+      </c>
+      <c r="F113" s="6">
+        <v>36</v>
+      </c>
+      <c r="G113" s="7">
+        <v>97</v>
+      </c>
+      <c r="H113" s="6">
+        <v>86</v>
+      </c>
+      <c r="I113" s="7">
+        <v>94</v>
+      </c>
+      <c r="J113" s="6">
+        <v>33</v>
+      </c>
+      <c r="K113"/>
+      <c r="L113"/>
+      <c r="M113" s="6">
+        <v>1</v>
+      </c>
+      <c r="N113" s="6">
+        <v>1</v>
+      </c>
+      <c r="O113" s="6">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
+      <c r="A114" s="6">
+        <v>202606040810</v>
+      </c>
+      <c r="B114" s="6">
+        <v>3</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D114" s="6">
+        <v>54</v>
+      </c>
+      <c r="E114" s="6">
+        <v>24.4</v>
+      </c>
+      <c r="F114" s="6">
+        <v>32</v>
+      </c>
+      <c r="G114" s="7">
+        <v>89</v>
+      </c>
+      <c r="H114" s="6">
+        <v>69</v>
+      </c>
+      <c r="I114" s="7">
+        <v>89</v>
+      </c>
+      <c r="J114" s="6">
+        <v>49</v>
+      </c>
+      <c r="K114" s="6">
+        <v>1</v>
+      </c>
+      <c r="L114"/>
+      <c r="M114" s="6">
+        <v>1</v>
+      </c>
+      <c r="N114" s="6">
+        <v>6</v>
+      </c>
+      <c r="O114" s="6">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15">
+      <c r="A115" s="6">
+        <v>202606040810</v>
+      </c>
+      <c r="B115" s="6">
+        <v>4</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D115" s="6">
+        <v>58</v>
+      </c>
+      <c r="E115" s="6">
+        <v>9.1</v>
+      </c>
+      <c r="F115" s="6">
+        <v>10</v>
+      </c>
+      <c r="G115" s="7">
+        <v>93</v>
+      </c>
+      <c r="H115" s="6">
+        <v>23</v>
+      </c>
+      <c r="I115" s="7">
+        <v>93</v>
+      </c>
+      <c r="J115" s="6">
+        <v>23</v>
+      </c>
+      <c r="K115"/>
+      <c r="L115"/>
+      <c r="M115"/>
+      <c r="N115" s="6">
+        <v>14</v>
+      </c>
+      <c r="O115" s="6">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15">
+      <c r="A116" s="6">
+        <v>202606040810</v>
+      </c>
+      <c r="B116" s="6">
+        <v>5</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D116" s="6">
+        <v>58</v>
+      </c>
+      <c r="E116" s="6">
+        <v>7.2</v>
+      </c>
+      <c r="F116" s="6">
+        <v>11</v>
+      </c>
+      <c r="G116" s="7">
+        <v>98</v>
+      </c>
+      <c r="H116" s="6">
+        <v>6</v>
+      </c>
+      <c r="I116" s="7">
+        <v>83</v>
+      </c>
+      <c r="J116" s="6">
+        <v>-23</v>
+      </c>
+      <c r="K116"/>
+      <c r="L116"/>
+      <c r="M116"/>
+      <c r="N116" s="6">
+        <v>15</v>
+      </c>
+      <c r="O116" s="6">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15">
+      <c r="A117" s="6">
+        <v>202606040810</v>
+      </c>
+      <c r="B117" s="6">
+        <v>6</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D117" s="6">
+        <v>54</v>
+      </c>
+      <c r="E117" s="6">
+        <v>4.2</v>
+      </c>
+      <c r="F117" s="6">
+        <v>2</v>
+      </c>
+      <c r="G117" s="7">
+        <v>99</v>
+      </c>
+      <c r="H117" s="6">
+        <v>20</v>
+      </c>
+      <c r="I117" s="7">
+        <v>88</v>
+      </c>
+      <c r="J117" s="6">
+        <v>-11</v>
+      </c>
+      <c r="K117"/>
+      <c r="L117"/>
+      <c r="M117"/>
+      <c r="N117" s="6">
+        <v>10</v>
+      </c>
+      <c r="O117" s="6">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15">
+      <c r="A118" s="6">
+        <v>202606040810</v>
+      </c>
+      <c r="B118" s="6">
+        <v>7</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D118" s="6">
+        <v>58</v>
+      </c>
+      <c r="E118" s="6">
+        <v>42.2</v>
+      </c>
+      <c r="F118" s="6">
+        <v>26</v>
+      </c>
+      <c r="G118" s="7">
+        <v>102</v>
+      </c>
+      <c r="H118" s="6">
+        <v>50</v>
+      </c>
+      <c r="I118" s="7">
+        <v>89</v>
+      </c>
+      <c r="J118" s="6">
+        <v>59</v>
+      </c>
+      <c r="K118"/>
+      <c r="L118"/>
+      <c r="M118"/>
+      <c r="N118" s="6">
+        <v>2</v>
+      </c>
+      <c r="O118" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15">
+      <c r="A119" s="6">
+        <v>202606040810</v>
+      </c>
+      <c r="B119" s="6">
+        <v>8</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D119" s="6">
+        <v>54</v>
+      </c>
+      <c r="E119" s="6">
+        <v>27.8</v>
+      </c>
+      <c r="F119" s="6">
+        <v>30</v>
+      </c>
+      <c r="G119" s="7">
+        <v>97</v>
+      </c>
+      <c r="H119" s="6">
+        <v>39</v>
+      </c>
+      <c r="I119" s="7">
+        <v>85</v>
+      </c>
+      <c r="J119" s="6">
+        <v>13</v>
+      </c>
+      <c r="K119"/>
+      <c r="L119"/>
+      <c r="M119" s="6">
+        <v>1</v>
+      </c>
+      <c r="N119" s="6">
+        <v>9</v>
+      </c>
+      <c r="O119" s="6">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15">
+      <c r="A120" s="6">
+        <v>202606040810</v>
+      </c>
+      <c r="B120" s="6">
+        <v>9</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D120" s="6">
+        <v>58</v>
+      </c>
+      <c r="E120" s="6">
+        <v>20.5</v>
+      </c>
+      <c r="F120" s="6">
+        <v>19</v>
+      </c>
+      <c r="G120" s="7">
+        <v>73</v>
+      </c>
+      <c r="H120" s="6">
+        <v>99</v>
+      </c>
+      <c r="I120" s="7">
+        <v>69</v>
+      </c>
+      <c r="J120" s="6">
+        <v>11</v>
+      </c>
+      <c r="K120" s="6">
+        <v>1</v>
+      </c>
+      <c r="L120"/>
+      <c r="M120"/>
+      <c r="N120" s="6">
+        <v>3</v>
+      </c>
+      <c r="O120" s="6">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15">
+      <c r="A121" s="6">
+        <v>202606040810</v>
+      </c>
+      <c r="B121" s="6">
+        <v>10</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D121" s="6">
+        <v>56</v>
+      </c>
+      <c r="E121" s="6">
+        <v>7.2</v>
+      </c>
+      <c r="F121" s="6">
+        <v>10</v>
+      </c>
+      <c r="G121" s="7">
+        <v>94</v>
+      </c>
+      <c r="H121" s="6">
+        <v>-1</v>
+      </c>
+      <c r="I121" s="7">
+        <v>91</v>
+      </c>
+      <c r="J121" s="6">
+        <v>1</v>
+      </c>
+      <c r="K121"/>
+      <c r="L121"/>
+      <c r="M121"/>
+      <c r="N121" s="6">
+        <v>11</v>
+      </c>
+      <c r="O121" s="6">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15">
+      <c r="A122" s="6">
+        <v>202606040810</v>
+      </c>
+      <c r="B122" s="6">
+        <v>11</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D122" s="6">
+        <v>56</v>
+      </c>
+      <c r="E122" s="6">
+        <v>10.4</v>
+      </c>
+      <c r="F122" s="6">
+        <v>24</v>
+      </c>
+      <c r="G122" s="7">
+        <v>84</v>
+      </c>
+      <c r="H122" s="6">
+        <v>30</v>
+      </c>
+      <c r="I122" s="7">
+        <v>93</v>
+      </c>
+      <c r="J122" s="6">
+        <v>50</v>
+      </c>
+      <c r="K122"/>
+      <c r="L122"/>
+      <c r="M122"/>
+      <c r="N122" s="6">
+        <v>13</v>
+      </c>
+      <c r="O122" s="6">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15">
+      <c r="A123" s="6">
+        <v>202606040810</v>
+      </c>
+      <c r="B123" s="6">
+        <v>12</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D123" s="6">
+        <v>54</v>
+      </c>
+      <c r="E123" s="6">
+        <v>13.4</v>
+      </c>
+      <c r="F123" s="6">
+        <v>15</v>
+      </c>
+      <c r="G123" s="7">
+        <v>94</v>
+      </c>
+      <c r="H123" s="6">
+        <v>55</v>
+      </c>
+      <c r="I123" s="7">
+        <v>84</v>
+      </c>
+      <c r="J123" s="6">
+        <v>18</v>
+      </c>
+      <c r="K123"/>
+      <c r="L123"/>
+      <c r="M123"/>
+      <c r="N123" s="6">
+        <v>8</v>
+      </c>
+      <c r="O123" s="6">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15">
+      <c r="A124" s="6">
+        <v>202606040810</v>
+      </c>
+      <c r="B124" s="6">
+        <v>13</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D124" s="6">
+        <v>58</v>
+      </c>
+      <c r="E124" s="6">
+        <v>12.4</v>
+      </c>
+      <c r="F124" s="6">
+        <v>18</v>
+      </c>
+      <c r="G124" s="7">
+        <v>93</v>
+      </c>
+      <c r="H124" s="6">
+        <v>21</v>
+      </c>
+      <c r="I124" s="7">
+        <v>81</v>
+      </c>
+      <c r="J124" s="6">
+        <v>17</v>
+      </c>
+      <c r="K124"/>
+      <c r="L124"/>
+      <c r="M124"/>
+      <c r="N124" s="6">
+        <v>16</v>
+      </c>
+      <c r="O124" s="6">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15">
+      <c r="A125" s="6">
+        <v>202606040810</v>
+      </c>
+      <c r="B125" s="6">
+        <v>14</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D125" s="6">
+        <v>56</v>
+      </c>
+      <c r="E125" s="6">
+        <v>21.4</v>
+      </c>
+      <c r="F125" s="6">
+        <v>30</v>
+      </c>
+      <c r="G125" s="7">
+        <v>87</v>
+      </c>
+      <c r="H125" s="6">
+        <v>36</v>
+      </c>
+      <c r="I125" s="7">
+        <v>85</v>
+      </c>
+      <c r="J125" s="6">
+        <v>34</v>
+      </c>
+      <c r="K125"/>
+      <c r="L125"/>
+      <c r="M125"/>
+      <c r="N125" s="6">
+        <v>5</v>
+      </c>
+      <c r="O125" s="6">
+        <v>9.7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15">
+      <c r="A126" s="6">
+        <v>202606040810</v>
+      </c>
+      <c r="B126" s="6">
+        <v>15</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D126" s="6">
+        <v>54</v>
+      </c>
+      <c r="E126" s="6">
+        <v>6.6</v>
+      </c>
+      <c r="F126" s="6">
+        <v>13</v>
+      </c>
+      <c r="G126" s="7">
+        <v>89</v>
+      </c>
+      <c r="H126" s="6">
+        <v>3</v>
+      </c>
+      <c r="I126" s="7">
+        <v>83</v>
+      </c>
+      <c r="J126" s="6">
+        <v>64</v>
+      </c>
+      <c r="K126"/>
+      <c r="L126"/>
+      <c r="M126"/>
+      <c r="N126" s="6">
+        <v>12</v>
+      </c>
+      <c r="O126" s="6">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15">
+      <c r="A127" s="6">
+        <v>202606040810</v>
+      </c>
+      <c r="B127" s="6">
+        <v>16</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D127" s="6">
+        <v>58</v>
+      </c>
+      <c r="E127" s="6">
+        <v>10.1</v>
+      </c>
+      <c r="F127" s="6">
+        <v>10</v>
+      </c>
+      <c r="G127" s="7">
+        <v>84</v>
+      </c>
+      <c r="H127" s="6">
+        <v>56</v>
+      </c>
+      <c r="I127" s="7">
+        <v>96</v>
+      </c>
+      <c r="J127" s="6">
+        <v>41</v>
+      </c>
+      <c r="K127"/>
+      <c r="L127"/>
+      <c r="M127" s="6">
+        <v>1</v>
+      </c>
+      <c r="N127" s="6">
+        <v>7</v>
+      </c>
+      <c r="O127" s="6">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15">
+      <c r="A128" s="6">
+        <v>202606040811</v>
+      </c>
+      <c r="B128" s="6">
+        <v>1</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D128" s="6">
+        <v>58</v>
+      </c>
+      <c r="E128" s="6">
+        <v>17.4</v>
+      </c>
+      <c r="F128" s="6">
+        <v>28</v>
+      </c>
+      <c r="G128" s="7">
+        <v>90</v>
+      </c>
+      <c r="H128" s="6">
+        <v>51</v>
+      </c>
+      <c r="I128" s="7">
+        <v>82</v>
+      </c>
+      <c r="J128" s="6">
+        <v>9</v>
+      </c>
+      <c r="K128"/>
+      <c r="L128"/>
+      <c r="M128"/>
+      <c r="N128" s="6">
+        <v>8</v>
+      </c>
+      <c r="O128" s="6">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15">
+      <c r="A129" s="6">
+        <v>202606040811</v>
+      </c>
+      <c r="B129" s="6">
+        <v>2</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D129" s="6">
+        <v>56</v>
+      </c>
+      <c r="E129" s="6">
+        <v>70.4</v>
+      </c>
+      <c r="F129" s="6">
+        <v>44</v>
+      </c>
+      <c r="G129" s="7">
+        <v>75</v>
+      </c>
+      <c r="H129" s="6">
+        <v>21</v>
+      </c>
+      <c r="I129" s="7">
+        <v>92</v>
+      </c>
+      <c r="J129" s="6">
+        <v>41</v>
+      </c>
+      <c r="K129"/>
+      <c r="L129"/>
+      <c r="M129"/>
+      <c r="N129" s="6">
+        <v>3</v>
+      </c>
+      <c r="O129" s="6">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15">
+      <c r="A130" s="6">
+        <v>202606040811</v>
+      </c>
+      <c r="B130" s="6">
+        <v>3</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D130" s="6">
+        <v>58</v>
+      </c>
+      <c r="E130" s="6">
+        <v>32</v>
+      </c>
+      <c r="F130" s="6">
+        <v>35</v>
+      </c>
+      <c r="G130" s="7">
+        <v>102</v>
+      </c>
+      <c r="H130" s="6">
+        <v>7</v>
+      </c>
+      <c r="I130" s="7">
+        <v>91</v>
+      </c>
+      <c r="J130" s="6">
+        <v>44</v>
+      </c>
+      <c r="K130" s="6">
+        <v>1</v>
+      </c>
+      <c r="L130"/>
+      <c r="M130" s="6">
+        <v>1</v>
+      </c>
+      <c r="N130" s="6">
+        <v>2</v>
+      </c>
+      <c r="O130" s="6">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15">
+      <c r="A131" s="6">
+        <v>202606040811</v>
+      </c>
+      <c r="B131" s="6">
+        <v>4</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D131" s="6">
+        <v>58</v>
+      </c>
+      <c r="E131" s="6">
+        <v>12</v>
+      </c>
+      <c r="F131" s="6">
+        <v>20</v>
+      </c>
+      <c r="G131" s="7">
+        <v>79</v>
+      </c>
+      <c r="H131" s="6">
+        <v>-84</v>
+      </c>
+      <c r="I131" s="7">
+        <v>92</v>
+      </c>
+      <c r="J131" s="6">
+        <v>47</v>
+      </c>
+      <c r="K131" s="6">
+        <v>1</v>
+      </c>
+      <c r="L131"/>
+      <c r="M131"/>
+      <c r="N131" s="6">
+        <v>4</v>
+      </c>
+      <c r="O131" s="6">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15">
+      <c r="A132" s="6">
+        <v>202606040811</v>
+      </c>
+      <c r="B132" s="6">
+        <v>5</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D132" s="6">
+        <v>58</v>
+      </c>
+      <c r="E132" s="6">
+        <v>4</v>
+      </c>
+      <c r="F132" s="6">
+        <v>4</v>
+      </c>
+      <c r="G132" s="7">
+        <v>88</v>
+      </c>
+      <c r="H132" s="6">
+        <v>-69</v>
+      </c>
+      <c r="I132" s="7">
+        <v>86</v>
+      </c>
+      <c r="J132" s="6">
+        <v>-41</v>
+      </c>
+      <c r="K132"/>
+      <c r="L132"/>
+      <c r="M132" s="6">
+        <v>1</v>
+      </c>
+      <c r="N132" s="6">
+        <v>10</v>
+      </c>
+      <c r="O132" s="6">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15">
+      <c r="A133" s="6">
+        <v>202606040811</v>
+      </c>
+      <c r="B133" s="6">
+        <v>6</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D133" s="6">
+        <v>58</v>
+      </c>
+      <c r="E133" s="6">
+        <v>6.4</v>
+      </c>
+      <c r="F133" s="6">
+        <v>10</v>
+      </c>
+      <c r="G133" s="7">
+        <v>87</v>
+      </c>
+      <c r="H133" s="6">
+        <v>-16</v>
+      </c>
+      <c r="I133" s="7">
+        <v>68</v>
+      </c>
+      <c r="J133" s="6">
+        <v>-48</v>
+      </c>
+      <c r="K133"/>
+      <c r="L133"/>
+      <c r="M133"/>
+      <c r="N133" s="6">
+        <v>14</v>
+      </c>
+      <c r="O133" s="6">
+        <v>74.5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15">
+      <c r="A134" s="6">
+        <v>202606040811</v>
+      </c>
+      <c r="B134" s="6">
+        <v>7</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D134" s="6">
+        <v>58</v>
+      </c>
+      <c r="E134" s="6">
+        <v>4.3</v>
+      </c>
+      <c r="F134" s="6">
+        <v>3</v>
+      </c>
+      <c r="G134" s="7">
+        <v>83</v>
+      </c>
+      <c r="H134" s="6">
+        <v>-30</v>
+      </c>
+      <c r="I134" s="7">
+        <v>88</v>
+      </c>
+      <c r="J134" s="6">
+        <v>28</v>
+      </c>
+      <c r="K134"/>
+      <c r="L134"/>
+      <c r="M134"/>
+      <c r="N134" s="6">
+        <v>13</v>
+      </c>
+      <c r="O134" s="6">
+        <v>67.3</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15">
+      <c r="A135" s="6">
+        <v>202606040811</v>
+      </c>
+      <c r="B135" s="6">
+        <v>8</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D135" s="6">
+        <v>58</v>
+      </c>
+      <c r="E135" s="6">
+        <v>38.2</v>
+      </c>
+      <c r="F135" s="6">
+        <v>36</v>
+      </c>
+      <c r="G135" s="7">
+        <v>77</v>
+      </c>
+      <c r="H135" s="6">
+        <v>28</v>
+      </c>
+      <c r="I135" s="7">
+        <v>95</v>
+      </c>
+      <c r="J135" s="6">
+        <v>42</v>
+      </c>
+      <c r="K135"/>
+      <c r="L135"/>
+      <c r="M135" s="6">
+        <v>1</v>
+      </c>
+      <c r="N135" s="6">
+        <v>1</v>
+      </c>
+      <c r="O135" s="6">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15">
+      <c r="A136" s="6">
+        <v>202606040811</v>
+      </c>
+      <c r="B136" s="6">
+        <v>9</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D136" s="6">
+        <v>58</v>
+      </c>
+      <c r="E136" s="6">
+        <v>4.1</v>
+      </c>
+      <c r="F136" s="6">
+        <v>1</v>
+      </c>
+      <c r="G136" s="7">
+        <v>85</v>
+      </c>
+      <c r="H136" s="6">
+        <v>-33</v>
+      </c>
+      <c r="I136" s="7">
+        <v>99</v>
+      </c>
+      <c r="J136" s="6">
+        <v>57</v>
+      </c>
+      <c r="K136"/>
+      <c r="L136"/>
+      <c r="M136"/>
+      <c r="N136" s="6">
+        <v>11</v>
+      </c>
+      <c r="O136" s="6">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15">
+      <c r="A137" s="6">
+        <v>202606040811</v>
+      </c>
+      <c r="B137" s="6">
+        <v>10</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D137" s="6">
+        <v>58</v>
+      </c>
+      <c r="E137" s="6">
+        <v>23.1</v>
+      </c>
+      <c r="F137" s="6">
+        <v>30</v>
+      </c>
+      <c r="G137" s="7">
+        <v>104</v>
+      </c>
+      <c r="H137" s="6">
+        <v>90</v>
+      </c>
+      <c r="I137" s="7">
+        <v>92</v>
+      </c>
+      <c r="J137" s="6">
+        <v>17</v>
+      </c>
+      <c r="K137"/>
+      <c r="L137"/>
+      <c r="M137"/>
+      <c r="N137" s="6">
+        <v>7</v>
+      </c>
+      <c r="O137" s="6">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15">
+      <c r="A138" s="6">
+        <v>202606040811</v>
+      </c>
+      <c r="B138" s="6">
+        <v>11</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D138" s="6">
+        <v>58</v>
+      </c>
+      <c r="E138" s="6">
+        <v>10.2</v>
+      </c>
+      <c r="F138" s="6">
+        <v>22</v>
+      </c>
+      <c r="G138" s="7">
+        <v>101</v>
+      </c>
+      <c r="H138" s="6">
+        <v>9</v>
+      </c>
+      <c r="I138" s="7">
+        <v>81</v>
+      </c>
+      <c r="J138" s="6">
+        <v>50</v>
+      </c>
+      <c r="K138"/>
+      <c r="L138"/>
+      <c r="M138"/>
+      <c r="N138" s="6">
+        <v>12</v>
+      </c>
+      <c r="O138" s="6">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15">
+      <c r="A139" s="6">
+        <v>202606040811</v>
+      </c>
+      <c r="B139" s="6">
+        <v>12</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D139" s="6">
+        <v>58</v>
+      </c>
+      <c r="E139" s="6">
+        <v>34.2</v>
+      </c>
+      <c r="F139" s="6">
+        <v>26</v>
+      </c>
+      <c r="G139" s="7">
+        <v>82</v>
+      </c>
+      <c r="H139" s="6">
+        <v>44</v>
+      </c>
+      <c r="I139" s="7">
+        <v>99</v>
+      </c>
+      <c r="J139" s="6">
+        <v>40</v>
+      </c>
+      <c r="K139"/>
+      <c r="L139"/>
+      <c r="M139"/>
+      <c r="N139" s="6">
+        <v>6</v>
+      </c>
+      <c r="O139" s="6">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15">
+      <c r="A140" s="6">
+        <v>202606040811</v>
+      </c>
+      <c r="B140" s="6">
+        <v>13</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D140" s="6">
+        <v>58</v>
+      </c>
+      <c r="E140" s="6">
+        <v>30.6</v>
+      </c>
+      <c r="F140" s="6">
+        <v>20</v>
+      </c>
+      <c r="G140" s="7">
+        <v>91</v>
+      </c>
+      <c r="H140" s="6">
+        <v>-80</v>
+      </c>
+      <c r="I140" s="7">
+        <v>96</v>
+      </c>
+      <c r="J140" s="6">
+        <v>21</v>
+      </c>
+      <c r="K140"/>
+      <c r="L140"/>
+      <c r="M140" s="6">
+        <v>1</v>
+      </c>
+      <c r="N140" s="6">
+        <v>5</v>
+      </c>
+      <c r="O140" s="6">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15">
+      <c r="A141" s="6">
+        <v>202606040811</v>
+      </c>
+      <c r="B141" s="6">
+        <v>14</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D141" s="6">
+        <v>56</v>
+      </c>
+      <c r="E141" s="6">
+        <v>13</v>
+      </c>
+      <c r="F141" s="6">
+        <v>16</v>
+      </c>
+      <c r="G141" s="7">
+        <v>81</v>
+      </c>
+      <c r="H141" s="6">
+        <v>-37</v>
+      </c>
+      <c r="I141" s="7">
+        <v>100</v>
+      </c>
+      <c r="J141" s="6">
+        <v>-27</v>
+      </c>
+      <c r="K141" s="6">
+        <v>1</v>
+      </c>
+      <c r="L141"/>
+      <c r="M141"/>
+      <c r="N141" s="6">
+        <v>9</v>
+      </c>
+      <c r="O141" s="6">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15">
+      <c r="A142" s="6">
+        <v>202606040812</v>
+      </c>
+      <c r="B142" s="6">
+        <v>1</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D142" s="6">
+        <v>54</v>
+      </c>
+      <c r="E142" s="6">
+        <v>15.9</v>
+      </c>
+      <c r="F142" s="6">
+        <v>24</v>
+      </c>
+      <c r="G142" s="7">
+        <v>84</v>
+      </c>
+      <c r="H142" s="6">
+        <v>53</v>
+      </c>
+      <c r="I142" s="7">
+        <v>83</v>
+      </c>
+      <c r="J142" s="6">
+        <v>-12</v>
+      </c>
+      <c r="K142"/>
+      <c r="L142"/>
+      <c r="M142" s="6">
+        <v>1</v>
+      </c>
+      <c r="N142" s="6">
+        <v>5</v>
+      </c>
+      <c r="O142" s="6">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15">
+      <c r="A143" s="6">
+        <v>202606040812</v>
+      </c>
+      <c r="B143" s="6">
+        <v>2</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D143" s="6">
+        <v>53</v>
+      </c>
+      <c r="E143" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="F143" s="6">
+        <v>1</v>
+      </c>
+      <c r="G143" s="7">
+        <v>55</v>
+      </c>
+      <c r="H143" s="6">
+        <v>-73</v>
+      </c>
+      <c r="I143" s="7">
+        <v>76</v>
+      </c>
+      <c r="J143" s="6">
+        <v>96</v>
+      </c>
+      <c r="K143"/>
+      <c r="L143"/>
+      <c r="M143"/>
+      <c r="N143" s="6">
+        <v>15</v>
+      </c>
+      <c r="O143" s="6">
+        <v>68.3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15">
+      <c r="A144" s="6">
+        <v>202606040812</v>
+      </c>
+      <c r="B144" s="6">
+        <v>3</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D144" s="6">
+        <v>58</v>
+      </c>
+      <c r="E144" s="6">
+        <v>5.4</v>
+      </c>
+      <c r="F144" s="6">
+        <v>4</v>
+      </c>
+      <c r="G144" s="7">
+        <v>76</v>
+      </c>
+      <c r="H144" s="6">
+        <v>12</v>
+      </c>
+      <c r="I144" s="7">
+        <v>94</v>
+      </c>
+      <c r="J144" s="6">
+        <v>-45</v>
+      </c>
+      <c r="K144"/>
+      <c r="L144"/>
+      <c r="M144"/>
+      <c r="N144" s="6">
+        <v>12</v>
+      </c>
+      <c r="O144" s="6">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15">
+      <c r="A145" s="6">
+        <v>202606040812</v>
+      </c>
+      <c r="B145" s="6">
+        <v>4</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D145" s="6">
+        <v>56</v>
+      </c>
+      <c r="E145" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="F145" s="6">
+        <v>2</v>
+      </c>
+      <c r="G145" s="7">
+        <v>67</v>
+      </c>
+      <c r="H145" s="6">
+        <v>-98</v>
+      </c>
+      <c r="I145" s="7">
+        <v>77</v>
+      </c>
+      <c r="J145" s="6">
+        <v>-26</v>
+      </c>
+      <c r="K145"/>
+      <c r="L145"/>
+      <c r="M145"/>
+      <c r="N145" s="6">
+        <v>13</v>
+      </c>
+      <c r="O145" s="6">
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15">
+      <c r="A146" s="6">
+        <v>202606040812</v>
+      </c>
+      <c r="B146" s="6">
+        <v>5</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D146" s="6">
+        <v>53</v>
+      </c>
+      <c r="E146" s="6">
+        <v>5.1</v>
+      </c>
+      <c r="F146" s="6">
+        <v>6</v>
+      </c>
+      <c r="G146" s="7">
+        <v>88</v>
+      </c>
+      <c r="H146" s="6">
+        <v>-40</v>
+      </c>
+      <c r="I146" s="7">
+        <v>76</v>
+      </c>
+      <c r="J146" s="6">
+        <v>-9</v>
+      </c>
+      <c r="K146"/>
+      <c r="L146"/>
+      <c r="M146"/>
+      <c r="N146" s="6">
+        <v>16</v>
+      </c>
+      <c r="O146" s="6">
+        <v>75.5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15">
+      <c r="A147" s="6">
+        <v>202606040812</v>
+      </c>
+      <c r="B147" s="6">
+        <v>6</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D147" s="6">
+        <v>56</v>
+      </c>
+      <c r="E147" s="6">
+        <v>36</v>
+      </c>
+      <c r="F147" s="6">
+        <v>34</v>
+      </c>
+      <c r="G147" s="7">
+        <v>103</v>
+      </c>
+      <c r="H147" s="6">
+        <v>-19</v>
+      </c>
+      <c r="I147" s="7">
+        <v>80</v>
+      </c>
+      <c r="J147" s="6">
+        <v>51</v>
+      </c>
+      <c r="K147"/>
+      <c r="L147"/>
+      <c r="M147" s="6">
+        <v>1</v>
+      </c>
+      <c r="N147" s="6">
+        <v>7</v>
+      </c>
+      <c r="O147" s="6">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15">
+      <c r="A148" s="6">
+        <v>202606040812</v>
+      </c>
+      <c r="B148" s="6">
+        <v>7</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D148" s="6">
+        <v>56</v>
+      </c>
+      <c r="E148" s="6">
+        <v>45.1</v>
+      </c>
+      <c r="F148" s="6">
+        <v>42</v>
+      </c>
+      <c r="G148" s="7">
+        <v>93</v>
+      </c>
+      <c r="H148" s="6">
+        <v>105</v>
+      </c>
+      <c r="I148" s="7">
+        <v>81</v>
+      </c>
+      <c r="J148" s="6">
+        <v>74</v>
+      </c>
+      <c r="K148" s="6">
+        <v>1</v>
+      </c>
+      <c r="L148"/>
+      <c r="M148"/>
+      <c r="N148" s="6">
+        <v>3</v>
+      </c>
+      <c r="O148" s="6">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15">
+      <c r="A149" s="6">
+        <v>202606040812</v>
+      </c>
+      <c r="B149" s="6">
+        <v>8</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D149" s="6">
+        <v>54</v>
+      </c>
+      <c r="E149" s="6">
+        <v>28.4</v>
+      </c>
+      <c r="F149" s="6">
+        <v>34</v>
+      </c>
+      <c r="G149" s="7">
+        <v>110</v>
+      </c>
+      <c r="H149" s="6">
+        <v>30</v>
+      </c>
+      <c r="I149" s="7">
+        <v>71</v>
+      </c>
+      <c r="J149" s="6">
+        <v>-19</v>
+      </c>
+      <c r="K149" s="6">
+        <v>1</v>
+      </c>
+      <c r="L149"/>
+      <c r="M149" s="6">
+        <v>1</v>
+      </c>
+      <c r="N149" s="6">
+        <v>1</v>
+      </c>
+      <c r="O149" s="6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15">
+      <c r="A150" s="6">
+        <v>202606040812</v>
+      </c>
+      <c r="B150" s="6">
+        <v>9</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D150" s="6">
+        <v>56</v>
+      </c>
+      <c r="E150" s="6">
+        <v>29.9</v>
+      </c>
+      <c r="F150" s="6">
+        <v>27</v>
+      </c>
+      <c r="G150" s="7">
+        <v>104</v>
+      </c>
+      <c r="H150" s="6">
+        <v>-9</v>
+      </c>
+      <c r="I150" s="7">
+        <v>86</v>
+      </c>
+      <c r="J150" s="6">
+        <v>-62</v>
+      </c>
+      <c r="K150"/>
+      <c r="L150"/>
+      <c r="M150" s="6">
+        <v>1</v>
+      </c>
+      <c r="N150" s="6">
+        <v>6</v>
+      </c>
+      <c r="O150" s="6">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15">
+      <c r="A151" s="6">
+        <v>202606040812</v>
+      </c>
+      <c r="B151" s="6">
+        <v>10</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D151" s="6">
+        <v>56</v>
+      </c>
+      <c r="E151" s="6">
+        <v>36.2</v>
+      </c>
+      <c r="F151" s="6">
+        <v>30</v>
+      </c>
+      <c r="G151" s="7">
+        <v>92</v>
+      </c>
+      <c r="H151" s="6">
+        <v>11</v>
+      </c>
+      <c r="I151" s="7">
+        <v>88</v>
+      </c>
+      <c r="J151" s="6">
+        <v>60</v>
+      </c>
+      <c r="K151" s="6">
+        <v>1</v>
+      </c>
+      <c r="L151"/>
+      <c r="M151" s="6">
+        <v>1</v>
+      </c>
+      <c r="N151" s="6">
+        <v>4</v>
+      </c>
+      <c r="O151" s="6">
+        <v>9.2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15">
+      <c r="A152" s="6">
+        <v>202606040812</v>
+      </c>
+      <c r="B152" s="6">
+        <v>11</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D152" s="6">
+        <v>56</v>
+      </c>
+      <c r="E152" s="6">
+        <v>29.7</v>
+      </c>
+      <c r="F152" s="6">
+        <v>30</v>
+      </c>
+      <c r="G152" s="7">
+        <v>101</v>
+      </c>
+      <c r="H152" s="6">
+        <v>8</v>
+      </c>
+      <c r="I152" s="7">
+        <v>86</v>
+      </c>
+      <c r="J152" s="6">
+        <v>-33</v>
+      </c>
+      <c r="K152"/>
+      <c r="L152"/>
+      <c r="M152"/>
+      <c r="N152" s="6">
+        <v>10</v>
+      </c>
+      <c r="O152" s="6">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15">
+      <c r="A153" s="6">
+        <v>202606040812</v>
+      </c>
+      <c r="B153" s="6">
+        <v>12</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D153" s="6">
+        <v>58</v>
+      </c>
+      <c r="E153" s="6">
+        <v>10.5</v>
+      </c>
+      <c r="F153" s="6">
+        <v>22</v>
+      </c>
+      <c r="G153" s="7">
+        <v>92</v>
+      </c>
+      <c r="H153" s="6">
+        <v>36</v>
+      </c>
+      <c r="I153" s="7">
+        <v>99</v>
+      </c>
+      <c r="J153" s="6">
+        <v>26</v>
+      </c>
+      <c r="K153"/>
+      <c r="L153"/>
+      <c r="M153"/>
+      <c r="N153" s="6">
+        <v>8</v>
+      </c>
+      <c r="O153" s="6">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15">
+      <c r="A154" s="6">
+        <v>202606040812</v>
+      </c>
+      <c r="B154" s="6">
+        <v>13</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D154" s="6">
+        <v>56</v>
+      </c>
+      <c r="E154" s="6">
+        <v>12.7</v>
+      </c>
+      <c r="F154" s="6">
+        <v>12</v>
+      </c>
+      <c r="G154" s="7">
+        <v>79</v>
+      </c>
+      <c r="H154" s="6">
+        <v>23</v>
+      </c>
+      <c r="I154" s="7">
+        <v>86</v>
+      </c>
+      <c r="J154" s="6">
+        <v>-12</v>
+      </c>
+      <c r="K154"/>
+      <c r="L154"/>
+      <c r="M154"/>
+      <c r="N154" s="6">
+        <v>2</v>
+      </c>
+      <c r="O154" s="6">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15">
+      <c r="A155" s="6">
+        <v>202606040812</v>
+      </c>
+      <c r="B155" s="6">
+        <v>14</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D155" s="6">
+        <v>58</v>
+      </c>
+      <c r="E155" s="6">
+        <v>24.7</v>
+      </c>
+      <c r="F155" s="6">
+        <v>28</v>
+      </c>
+      <c r="G155" s="7">
+        <v>95</v>
+      </c>
+      <c r="H155" s="6">
+        <v>75</v>
+      </c>
+      <c r="I155" s="7">
+        <v>87</v>
+      </c>
+      <c r="J155" s="6">
+        <v>11</v>
+      </c>
+      <c r="K155"/>
+      <c r="L155"/>
+      <c r="M155"/>
+      <c r="N155" s="6">
+        <v>11</v>
+      </c>
+      <c r="O155" s="6">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15">
+      <c r="A156" s="6">
+        <v>202606040812</v>
+      </c>
+      <c r="B156" s="6">
+        <v>15</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D156" s="6">
+        <v>55</v>
+      </c>
+      <c r="E156" s="6">
+        <v>6.2</v>
+      </c>
+      <c r="F156" s="6">
+        <v>9</v>
+      </c>
+      <c r="G156"/>
+      <c r="H156"/>
+      <c r="I156"/>
+      <c r="J156"/>
+      <c r="K156"/>
+      <c r="L156"/>
+      <c r="M156"/>
+      <c r="N156" s="6">
+        <v>9</v>
+      </c>
+      <c r="O156" s="6">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15">
+      <c r="A157" s="6">
+        <v>202606040812</v>
+      </c>
+      <c r="B157" s="6">
+        <v>16</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D157" s="6">
+        <v>58</v>
+      </c>
+      <c r="E157" s="6">
+        <v>6.8</v>
+      </c>
+      <c r="F157" s="6">
+        <v>6</v>
+      </c>
+      <c r="G157" s="7">
+        <v>79</v>
+      </c>
+      <c r="H157" s="6">
+        <v>-38</v>
+      </c>
+      <c r="I157" s="7">
+        <v>80</v>
+      </c>
+      <c r="J157" s="6">
+        <v>-12</v>
+      </c>
+      <c r="K157"/>
+      <c r="L157"/>
+      <c r="M157"/>
+      <c r="N157" s="6">
+        <v>14</v>
+      </c>
+      <c r="O157" s="6">
+        <v>67.3</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15">
+      <c r="A158" s="6">
+        <v>202609040804</v>
+      </c>
+      <c r="B158" s="6">
+        <v>1</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D158" s="6">
+        <v>55</v>
+      </c>
+      <c r="E158" s="6">
+        <v>7</v>
+      </c>
+      <c r="F158" s="6">
+        <v>12</v>
+      </c>
+      <c r="G158"/>
+      <c r="H158"/>
+      <c r="I158"/>
+      <c r="J158"/>
+      <c r="K158"/>
+      <c r="L158"/>
+      <c r="M158"/>
+      <c r="N158"/>
+      <c r="O158"/>
+    </row>
+    <row r="159" spans="1:15">
+      <c r="A159" s="6">
+        <v>202609040804</v>
+      </c>
+      <c r="B159" s="6">
+        <v>2</v>
+      </c>
+      <c r="C159" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D159" s="6">
+        <v>55</v>
+      </c>
+      <c r="E159" s="6">
+        <v>19.2</v>
+      </c>
+      <c r="F159" s="6">
+        <v>17</v>
+      </c>
+      <c r="G159"/>
+      <c r="H159"/>
+      <c r="I159"/>
+      <c r="J159"/>
+      <c r="K159" s="6">
+        <v>1</v>
+      </c>
+      <c r="L159"/>
+      <c r="M159"/>
+      <c r="N159"/>
+      <c r="O159"/>
+    </row>
+    <row r="160" spans="1:15">
+      <c r="A160" s="6">
+        <v>202609040804</v>
+      </c>
+      <c r="B160" s="6">
+        <v>3</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D160" s="6">
+        <v>55</v>
+      </c>
+      <c r="E160" s="6">
+        <v>8.4</v>
+      </c>
+      <c r="F160" s="6">
+        <v>12</v>
+      </c>
+      <c r="G160"/>
+      <c r="H160"/>
+      <c r="I160"/>
+      <c r="J160"/>
+      <c r="K160" s="6">
+        <v>1</v>
+      </c>
+      <c r="L160"/>
+      <c r="M160"/>
+      <c r="N160"/>
+      <c r="O160"/>
+    </row>
+    <row r="161" spans="1:15">
+      <c r="A161" s="6">
+        <v>202609040804</v>
+      </c>
+      <c r="B161" s="6">
+        <v>4</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D161" s="6">
+        <v>55</v>
+      </c>
+      <c r="E161" s="6">
+        <v>16</v>
+      </c>
+      <c r="F161" s="6">
+        <v>21</v>
+      </c>
+      <c r="G161"/>
+      <c r="H161"/>
+      <c r="I161"/>
+      <c r="J161"/>
+      <c r="K161" s="6">
+        <v>1</v>
+      </c>
+      <c r="L161"/>
+      <c r="M161"/>
+      <c r="N161"/>
+      <c r="O161"/>
+    </row>
+    <row r="162" spans="1:15">
+      <c r="A162" s="6">
+        <v>202609040804</v>
+      </c>
+      <c r="B162" s="6">
+        <v>5</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D162" s="6">
+        <v>55</v>
+      </c>
+      <c r="E162" s="6">
+        <v>4.7</v>
+      </c>
+      <c r="F162" s="6">
+        <v>9</v>
+      </c>
+      <c r="G162"/>
+      <c r="H162"/>
+      <c r="I162"/>
+      <c r="J162"/>
+      <c r="K162"/>
+      <c r="L162"/>
+      <c r="M162"/>
+      <c r="N162"/>
+      <c r="O162"/>
+    </row>
+    <row r="163" spans="1:15">
+      <c r="A163" s="6">
+        <v>202609040804</v>
+      </c>
+      <c r="B163" s="6">
+        <v>6</v>
+      </c>
+      <c r="C163" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="D163" s="6">
+        <v>55</v>
+      </c>
+      <c r="E163" s="6">
+        <v>21</v>
+      </c>
+      <c r="F163" s="6">
+        <v>26</v>
+      </c>
+      <c r="G163"/>
+      <c r="H163"/>
+      <c r="I163"/>
+      <c r="J163"/>
+      <c r="K163"/>
+      <c r="L163"/>
+      <c r="M163"/>
+      <c r="N163"/>
+      <c r="O163"/>
+    </row>
+    <row r="164" spans="1:15">
+      <c r="A164" s="6">
+        <v>202609040804</v>
+      </c>
+      <c r="B164" s="6">
+        <v>7</v>
+      </c>
+      <c r="C164" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="D164" s="6">
+        <v>54</v>
+      </c>
+      <c r="E164" s="6">
+        <v>35</v>
+      </c>
+      <c r="F164" s="6">
+        <v>24</v>
+      </c>
+      <c r="G164"/>
+      <c r="H164"/>
+      <c r="I164"/>
+      <c r="J164"/>
+      <c r="K164"/>
+      <c r="L164"/>
+      <c r="M164" s="6">
+        <v>1</v>
+      </c>
+      <c r="N164"/>
+      <c r="O164"/>
+    </row>
+    <row r="165" spans="1:15">
+      <c r="A165" s="6">
+        <v>202609040804</v>
+      </c>
+      <c r="B165" s="6">
+        <v>8</v>
+      </c>
+      <c r="C165" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D165" s="6">
+        <v>55</v>
+      </c>
+      <c r="E165" s="6">
+        <v>24.3</v>
+      </c>
+      <c r="F165" s="6">
+        <v>22</v>
+      </c>
+      <c r="G165"/>
+      <c r="H165"/>
+      <c r="I165"/>
+      <c r="J165"/>
+      <c r="K165"/>
+      <c r="L165"/>
+      <c r="M165" s="6">
+        <v>1</v>
+      </c>
+      <c r="N165"/>
+      <c r="O165"/>
+    </row>
+    <row r="166" spans="1:15">
+      <c r="A166" s="6">
+        <v>202609040804</v>
+      </c>
+      <c r="B166" s="6">
+        <v>9</v>
+      </c>
+      <c r="C166" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D166" s="6">
+        <v>55</v>
+      </c>
+      <c r="E166" s="6">
+        <v>23.7</v>
+      </c>
+      <c r="F166" s="6">
+        <v>20</v>
+      </c>
+      <c r="G166"/>
+      <c r="H166"/>
+      <c r="I166"/>
+      <c r="J166"/>
+      <c r="K166"/>
+      <c r="L166"/>
+      <c r="M166" s="6">
+        <v>1</v>
+      </c>
+      <c r="N166"/>
+      <c r="O166"/>
+    </row>
+    <row r="167" spans="1:15">
+      <c r="A167" s="6">
+        <v>202609040804</v>
+      </c>
+      <c r="B167" s="6">
+        <v>10</v>
+      </c>
+      <c r="C167" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D167" s="6">
+        <v>55</v>
+      </c>
+      <c r="E167" s="6">
+        <v>37.4</v>
+      </c>
+      <c r="F167" s="6">
+        <v>22</v>
+      </c>
+      <c r="G167"/>
+      <c r="H167"/>
+      <c r="I167"/>
+      <c r="J167"/>
+      <c r="K167"/>
+      <c r="L167"/>
+      <c r="M167" s="6">
+        <v>1</v>
+      </c>
+      <c r="N167"/>
+      <c r="O167"/>
+    </row>
+    <row r="168" spans="1:15">
+      <c r="A168" s="6">
+        <v>202609040804</v>
+      </c>
+      <c r="B168" s="6">
+        <v>11</v>
+      </c>
+      <c r="C168" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="D168" s="6">
+        <v>55</v>
+      </c>
+      <c r="E168" s="6">
+        <v>5.2</v>
+      </c>
+      <c r="F168" s="6">
+        <v>10</v>
+      </c>
+      <c r="G168"/>
+      <c r="H168"/>
+      <c r="I168"/>
+      <c r="J168"/>
+      <c r="K168"/>
+      <c r="L168"/>
+      <c r="M168"/>
+      <c r="N168"/>
+      <c r="O168"/>
+    </row>
+    <row r="169" spans="1:15">
+      <c r="A169" s="6">
+        <v>202609040804</v>
+      </c>
+      <c r="B169" s="6">
+        <v>12</v>
+      </c>
+      <c r="C169" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D169" s="6">
+        <v>55</v>
+      </c>
+      <c r="E169" s="6">
+        <v>6.3</v>
+      </c>
+      <c r="F169" s="6">
+        <v>12</v>
+      </c>
+      <c r="G169"/>
+      <c r="H169"/>
+      <c r="I169"/>
+      <c r="J169"/>
+      <c r="K169"/>
+      <c r="L169"/>
+      <c r="M169" s="6">
+        <v>1</v>
+      </c>
+      <c r="N169"/>
+      <c r="O169"/>
+    </row>
+    <row r="170" spans="1:15">
+      <c r="A170" s="6">
+        <v>202609040804</v>
+      </c>
+      <c r="B170" s="6">
+        <v>13</v>
+      </c>
+      <c r="C170" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D170" s="6">
+        <v>55</v>
+      </c>
+      <c r="E170" s="6">
+        <v>41.2</v>
+      </c>
+      <c r="F170" s="6">
+        <v>28</v>
+      </c>
+      <c r="G170"/>
+      <c r="H170"/>
+      <c r="I170"/>
+      <c r="J170"/>
+      <c r="K170"/>
+      <c r="L170"/>
+      <c r="M170"/>
+      <c r="N170"/>
+      <c r="O170"/>
+    </row>
+    <row r="171" spans="1:15">
+      <c r="A171" s="6">
+        <v>202609040804</v>
+      </c>
+      <c r="B171" s="6">
+        <v>14</v>
+      </c>
+      <c r="C171" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="D171" s="6">
+        <v>55</v>
+      </c>
+      <c r="E171" s="6">
+        <v>35.9</v>
+      </c>
+      <c r="F171" s="6">
+        <v>24</v>
+      </c>
+      <c r="G171"/>
+      <c r="H171"/>
+      <c r="I171"/>
+      <c r="J171"/>
+      <c r="K171"/>
+      <c r="L171"/>
+      <c r="M171"/>
+      <c r="N171"/>
+      <c r="O171"/>
+    </row>
+    <row r="172" spans="1:15">
+      <c r="A172" s="6">
+        <v>202609040804</v>
+      </c>
+      <c r="B172" s="6">
+        <v>15</v>
+      </c>
+      <c r="C172" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D172" s="6">
+        <v>55</v>
+      </c>
+      <c r="E172" s="6">
+        <v>14.7</v>
+      </c>
+      <c r="F172" s="6">
+        <v>19</v>
+      </c>
+      <c r="G172"/>
+      <c r="H172"/>
+      <c r="I172"/>
+      <c r="J172"/>
+      <c r="K172"/>
+      <c r="L172"/>
+      <c r="M172" s="6">
+        <v>1</v>
+      </c>
+      <c r="N172"/>
+      <c r="O172"/>
+    </row>
+    <row r="173" spans="1:15">
+      <c r="A173" s="6">
+        <v>202609040806</v>
+      </c>
+      <c r="B173" s="6">
+        <v>1</v>
+      </c>
+      <c r="C173" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="D173" s="6">
+        <v>58</v>
+      </c>
+      <c r="E173" s="6">
+        <v>4.2</v>
+      </c>
+      <c r="F173" s="6">
+        <v>6</v>
+      </c>
+      <c r="G173" s="7">
+        <v>59</v>
+      </c>
+      <c r="H173" s="6">
+        <v>-10</v>
+      </c>
+      <c r="I173" s="7">
+        <v>67</v>
+      </c>
+      <c r="J173" s="6">
+        <v>-17</v>
+      </c>
+      <c r="K173"/>
+      <c r="L173"/>
+      <c r="M173"/>
+      <c r="N173" s="6">
+        <v>14</v>
+      </c>
+      <c r="O173" s="6">
+        <v>94.3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15">
+      <c r="A174" s="6">
+        <v>202609040806</v>
+      </c>
+      <c r="B174" s="6">
+        <v>2</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D174" s="6">
+        <v>55</v>
+      </c>
+      <c r="E174" s="6">
+        <v>37.2</v>
+      </c>
+      <c r="F174" s="6">
+        <v>32</v>
+      </c>
+      <c r="G174" s="7">
+        <v>76</v>
+      </c>
+      <c r="H174" s="6">
+        <v>22</v>
+      </c>
+      <c r="I174" s="7">
+        <v>85</v>
+      </c>
+      <c r="J174" s="6">
+        <v>85</v>
+      </c>
+      <c r="K174"/>
+      <c r="L174"/>
+      <c r="M174"/>
+      <c r="N174" s="6">
+        <v>7</v>
+      </c>
+      <c r="O174" s="6">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15">
+      <c r="A175" s="6">
+        <v>202609040806</v>
+      </c>
+      <c r="B175" s="6">
+        <v>3</v>
+      </c>
+      <c r="C175" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D175" s="6">
+        <v>55</v>
+      </c>
+      <c r="E175" s="6">
+        <v>16.8</v>
+      </c>
+      <c r="F175" s="6">
+        <v>24</v>
+      </c>
+      <c r="G175" s="7">
+        <v>85</v>
+      </c>
+      <c r="H175" s="6">
+        <v>157</v>
+      </c>
+      <c r="I175" s="7">
+        <v>97</v>
+      </c>
+      <c r="J175" s="6">
+        <v>-49</v>
+      </c>
+      <c r="K175" s="6">
+        <v>1</v>
+      </c>
+      <c r="L175"/>
+      <c r="M175"/>
+      <c r="N175" s="6">
+        <v>9</v>
+      </c>
+      <c r="O175" s="6">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15">
+      <c r="A176" s="6">
+        <v>202609040806</v>
+      </c>
+      <c r="B176" s="6">
+        <v>4</v>
+      </c>
+      <c r="C176" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D176" s="6">
+        <v>58</v>
+      </c>
+      <c r="E176" s="6">
+        <v>9.8</v>
+      </c>
+      <c r="F176" s="6">
+        <v>14</v>
+      </c>
+      <c r="G176" s="7">
+        <v>82</v>
+      </c>
+      <c r="H176" s="6">
+        <v>32</v>
+      </c>
+      <c r="I176" s="7">
+        <v>80</v>
+      </c>
+      <c r="J176" s="6">
+        <v>-39</v>
+      </c>
+      <c r="K176"/>
+      <c r="L176"/>
+      <c r="M176"/>
+      <c r="N176" s="6">
+        <v>3</v>
+      </c>
+      <c r="O176" s="6">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15">
+      <c r="A177" s="6">
+        <v>202609040806</v>
+      </c>
+      <c r="B177" s="6">
+        <v>5</v>
+      </c>
+      <c r="C177" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D177" s="6">
+        <v>58</v>
+      </c>
+      <c r="E177" s="6">
+        <v>6.5</v>
+      </c>
+      <c r="F177" s="6">
+        <v>1</v>
+      </c>
+      <c r="G177" s="7">
+        <v>48</v>
+      </c>
+      <c r="H177" s="6">
+        <v>-153</v>
+      </c>
+      <c r="I177" s="7">
+        <v>71</v>
+      </c>
+      <c r="J177" s="6">
+        <v>94</v>
+      </c>
+      <c r="K177"/>
+      <c r="L177"/>
+      <c r="M177"/>
+      <c r="N177" s="6">
+        <v>13</v>
+      </c>
+      <c r="O177" s="6">
+        <v>85.7</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15">
+      <c r="A178" s="6">
+        <v>202609040806</v>
+      </c>
+      <c r="B178" s="6">
+        <v>6</v>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D178" s="6">
+        <v>58</v>
+      </c>
+      <c r="E178" s="6">
+        <v>4</v>
+      </c>
+      <c r="F178" s="6">
+        <v>4</v>
+      </c>
+      <c r="G178" s="7">
+        <v>63</v>
+      </c>
+      <c r="H178" s="6">
+        <v>-190</v>
+      </c>
+      <c r="I178" s="7">
+        <v>79</v>
+      </c>
+      <c r="J178" s="6">
+        <v>-85</v>
+      </c>
+      <c r="K178"/>
+      <c r="L178"/>
+      <c r="M178"/>
+      <c r="N178" s="6">
+        <v>16</v>
+      </c>
+      <c r="O178" s="6">
+        <v>104.8</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15">
+      <c r="A179" s="6">
+        <v>202609040806</v>
+      </c>
+      <c r="B179" s="6">
+        <v>7</v>
+      </c>
+      <c r="C179" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D179" s="6">
+        <v>58</v>
+      </c>
+      <c r="E179" s="6">
+        <v>4</v>
+      </c>
+      <c r="F179" s="6">
+        <v>4</v>
+      </c>
+      <c r="G179" s="7">
+        <v>71</v>
+      </c>
+      <c r="H179" s="6">
+        <v>-51</v>
+      </c>
+      <c r="I179" s="7">
+        <v>63</v>
+      </c>
+      <c r="J179" s="6">
+        <v>-50</v>
+      </c>
+      <c r="K179"/>
+      <c r="L179"/>
+      <c r="M179"/>
+      <c r="N179" s="6">
+        <v>15</v>
+      </c>
+      <c r="O179" s="6">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15">
+      <c r="A180" s="6">
+        <v>202609040806</v>
+      </c>
+      <c r="B180" s="6">
+        <v>8</v>
+      </c>
+      <c r="C180" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D180" s="6">
+        <v>55</v>
+      </c>
+      <c r="E180" s="6">
+        <v>41</v>
+      </c>
+      <c r="F180" s="6">
+        <v>39</v>
+      </c>
+      <c r="G180" s="7">
+        <v>89</v>
+      </c>
+      <c r="H180" s="6">
+        <v>-18</v>
+      </c>
+      <c r="I180" s="7">
+        <v>79</v>
+      </c>
+      <c r="J180" s="6">
+        <v>37</v>
+      </c>
+      <c r="K180"/>
+      <c r="L180"/>
+      <c r="M180" s="6">
+        <v>1</v>
+      </c>
+      <c r="N180" s="6">
+        <v>4</v>
+      </c>
+      <c r="O180" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15">
+      <c r="A181" s="6">
+        <v>202609040806</v>
+      </c>
+      <c r="B181" s="6">
+        <v>9</v>
+      </c>
+      <c r="C181" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D181" s="6">
+        <v>58</v>
+      </c>
+      <c r="E181" s="6">
+        <v>22.8</v>
+      </c>
+      <c r="F181" s="6">
+        <v>24</v>
+      </c>
+      <c r="G181" s="7">
+        <v>79</v>
+      </c>
+      <c r="H181" s="6">
+        <v>-33</v>
+      </c>
+      <c r="I181" s="7">
+        <v>86</v>
+      </c>
+      <c r="J181" s="6">
+        <v>64</v>
+      </c>
+      <c r="K181"/>
+      <c r="L181"/>
+      <c r="M181"/>
+      <c r="N181" s="6">
+        <v>6</v>
+      </c>
+      <c r="O181" s="6">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15">
+      <c r="A182" s="6">
+        <v>202609040806</v>
+      </c>
+      <c r="B182" s="6">
+        <v>10</v>
+      </c>
+      <c r="C182" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D182" s="6">
+        <v>55</v>
+      </c>
+      <c r="E182" s="6">
+        <v>8.3</v>
+      </c>
+      <c r="F182" s="6">
+        <v>13</v>
+      </c>
+      <c r="G182" s="7">
+        <v>73</v>
+      </c>
+      <c r="H182" s="6">
+        <v>-153</v>
+      </c>
+      <c r="I182" s="7">
+        <v>104</v>
+      </c>
+      <c r="J182" s="6">
+        <v>40</v>
+      </c>
+      <c r="K182"/>
+      <c r="L182"/>
+      <c r="M182"/>
+      <c r="N182" s="6">
+        <v>11</v>
+      </c>
+      <c r="O182" s="6">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15">
+      <c r="A183" s="6">
+        <v>202609040806</v>
+      </c>
+      <c r="B183" s="6">
+        <v>11</v>
+      </c>
+      <c r="C183" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D183" s="6">
+        <v>58</v>
+      </c>
+      <c r="E183" s="6">
+        <v>36.2</v>
+      </c>
+      <c r="F183" s="6">
+        <v>44</v>
+      </c>
+      <c r="G183" s="7">
+        <v>86</v>
+      </c>
+      <c r="H183" s="6">
+        <v>17</v>
+      </c>
+      <c r="I183" s="7">
+        <v>87</v>
+      </c>
+      <c r="J183" s="6">
+        <v>55</v>
+      </c>
+      <c r="K183" s="6">
+        <v>1</v>
+      </c>
+      <c r="L183"/>
+      <c r="M183" s="6">
+        <v>1</v>
+      </c>
+      <c r="N183" s="6">
+        <v>2</v>
+      </c>
+      <c r="O183" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15">
+      <c r="A184" s="6">
+        <v>202609040806</v>
+      </c>
+      <c r="B184" s="6">
+        <v>12</v>
+      </c>
+      <c r="C184" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D184" s="6">
+        <v>55</v>
+      </c>
+      <c r="E184" s="6">
+        <v>13</v>
+      </c>
+      <c r="F184" s="6">
+        <v>25</v>
+      </c>
+      <c r="G184" s="7">
+        <v>74</v>
+      </c>
+      <c r="H184" s="6">
+        <v>28</v>
+      </c>
+      <c r="I184" s="7">
+        <v>67</v>
+      </c>
+      <c r="J184" s="6">
+        <v>39</v>
+      </c>
+      <c r="K184"/>
+      <c r="L184"/>
+      <c r="M184" s="6">
+        <v>1</v>
+      </c>
+      <c r="N184" s="6">
+        <v>10</v>
+      </c>
+      <c r="O184" s="6">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15">
+      <c r="A185" s="6">
+        <v>202609040806</v>
+      </c>
+      <c r="B185" s="6">
+        <v>13</v>
+      </c>
+      <c r="C185" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D185" s="6">
+        <v>55</v>
+      </c>
+      <c r="E185" s="6">
+        <v>47.9</v>
+      </c>
+      <c r="F185" s="6">
+        <v>50</v>
+      </c>
+      <c r="G185" s="7">
+        <v>80</v>
+      </c>
+      <c r="H185" s="6">
+        <v>25</v>
+      </c>
+      <c r="I185" s="7">
+        <v>55</v>
+      </c>
+      <c r="J185" s="6">
+        <v>-68</v>
+      </c>
+      <c r="K185"/>
+      <c r="L185"/>
+      <c r="M185"/>
+      <c r="N185" s="6">
+        <v>1</v>
+      </c>
+      <c r="O185" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15">
+      <c r="A186" s="6">
+        <v>202609040806</v>
+      </c>
+      <c r="B186" s="6">
+        <v>14</v>
+      </c>
+      <c r="C186" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="D186" s="6">
+        <v>55</v>
+      </c>
+      <c r="E186" s="6">
+        <v>4.7</v>
+      </c>
+      <c r="F186" s="6">
+        <v>20</v>
+      </c>
+      <c r="G186" s="7">
+        <v>64</v>
+      </c>
+      <c r="H186" s="6">
+        <v>28</v>
+      </c>
+      <c r="I186" s="7">
+        <v>54</v>
+      </c>
+      <c r="J186" s="6">
+        <v>-64</v>
+      </c>
+      <c r="K186"/>
+      <c r="L186"/>
+      <c r="M186"/>
+      <c r="N186" s="6">
+        <v>12</v>
+      </c>
+      <c r="O186" s="6">
+        <v>52.4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15">
+      <c r="A187" s="6">
+        <v>202609040806</v>
+      </c>
+      <c r="B187" s="6">
+        <v>15</v>
+      </c>
+      <c r="C187" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D187" s="6">
+        <v>52</v>
+      </c>
+      <c r="E187" s="6">
+        <v>28.9</v>
+      </c>
+      <c r="F187" s="6">
+        <v>28</v>
+      </c>
+      <c r="G187" s="7">
+        <v>90</v>
+      </c>
+      <c r="H187" s="6">
+        <v>24</v>
+      </c>
+      <c r="I187" s="7">
+        <v>90</v>
+      </c>
+      <c r="J187" s="6">
+        <v>24</v>
+      </c>
+      <c r="K187"/>
+      <c r="L187"/>
+      <c r="M187" s="6">
+        <v>1</v>
+      </c>
+      <c r="N187" s="6">
+        <v>5</v>
+      </c>
+      <c r="O187" s="6">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15">
+      <c r="A188" s="6">
+        <v>202609040806</v>
+      </c>
+      <c r="B188" s="6">
+        <v>16</v>
+      </c>
+      <c r="C188" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D188" s="6">
+        <v>53</v>
+      </c>
+      <c r="E188" s="6">
+        <v>14.8</v>
+      </c>
+      <c r="F188" s="6">
+        <v>20</v>
+      </c>
+      <c r="G188" s="7">
+        <v>77</v>
+      </c>
+      <c r="H188" s="6">
+        <v>-80</v>
+      </c>
+      <c r="I188" s="7">
+        <v>79</v>
+      </c>
+      <c r="J188" s="6">
+        <v>-27</v>
+      </c>
+      <c r="K188" s="6">
+        <v>1</v>
+      </c>
+      <c r="L188"/>
+      <c r="M188" s="6">
+        <v>1</v>
+      </c>
+      <c r="N188" s="6">
+        <v>8</v>
+      </c>
+      <c r="O188" s="6">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15">
+      <c r="A189" s="6">
+        <v>202609040811</v>
+      </c>
+      <c r="B189" s="6">
+        <v>1</v>
+      </c>
+      <c r="C189" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="D189" s="6">
+        <v>57</v>
+      </c>
+      <c r="E189" s="6">
+        <v>13.4</v>
+      </c>
+      <c r="F189" s="6">
+        <v>16</v>
+      </c>
+      <c r="G189" s="7">
+        <v>92</v>
+      </c>
+      <c r="H189" s="6">
+        <v>-59</v>
+      </c>
+      <c r="I189" s="7">
+        <v>93</v>
+      </c>
+      <c r="J189" s="6">
+        <v>-132</v>
+      </c>
+      <c r="K189" s="6">
+        <v>1</v>
+      </c>
+      <c r="L189"/>
+      <c r="M189" s="6">
+        <v>1</v>
+      </c>
+      <c r="N189" s="6">
+        <v>7</v>
+      </c>
+      <c r="O189" s="6">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15">
+      <c r="A190" s="6">
+        <v>202609040811</v>
+      </c>
+      <c r="B190" s="6">
+        <v>2</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D190" s="6">
+        <v>57</v>
+      </c>
+      <c r="E190" s="6">
+        <v>17.5</v>
+      </c>
+      <c r="F190" s="6">
+        <v>17</v>
+      </c>
+      <c r="G190" s="7">
+        <v>89</v>
+      </c>
+      <c r="H190" s="6">
+        <v>51</v>
+      </c>
+      <c r="I190" s="7">
+        <v>93</v>
+      </c>
+      <c r="J190" s="6">
+        <v>-44</v>
+      </c>
+      <c r="K190"/>
+      <c r="L190"/>
+      <c r="M190"/>
+      <c r="N190" s="6">
+        <v>11</v>
+      </c>
+      <c r="O190" s="6">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15">
+      <c r="A191" s="6">
+        <v>202609040811</v>
+      </c>
+      <c r="B191" s="6">
+        <v>3</v>
+      </c>
+      <c r="C191" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D191" s="6">
+        <v>57</v>
+      </c>
+      <c r="E191" s="6">
+        <v>13.8</v>
+      </c>
+      <c r="F191" s="6">
+        <v>19</v>
+      </c>
+      <c r="G191" s="7">
+        <v>93</v>
+      </c>
+      <c r="H191" s="6">
+        <v>35</v>
+      </c>
+      <c r="I191" s="7">
+        <v>85</v>
+      </c>
+      <c r="J191" s="6">
+        <v>-24</v>
+      </c>
+      <c r="K191"/>
+      <c r="L191"/>
+      <c r="M191" s="6">
+        <v>1</v>
+      </c>
+      <c r="N191" s="6">
+        <v>9</v>
+      </c>
+      <c r="O191" s="6">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15">
+      <c r="A192" s="6">
+        <v>202609040811</v>
+      </c>
+      <c r="B192" s="6">
+        <v>4</v>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D192" s="6">
+        <v>55</v>
+      </c>
+      <c r="E192" s="6">
+        <v>4.3</v>
+      </c>
+      <c r="F192" s="6">
+        <v>1</v>
+      </c>
+      <c r="G192" s="7">
+        <v>90</v>
+      </c>
+      <c r="H192" s="6">
+        <v>-77</v>
+      </c>
+      <c r="I192" s="7">
+        <v>95</v>
+      </c>
+      <c r="J192" s="6">
+        <v>-76</v>
+      </c>
+      <c r="K192"/>
+      <c r="L192"/>
+      <c r="M192"/>
+      <c r="N192" s="6">
+        <v>16</v>
+      </c>
+      <c r="O192" s="6">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15">
+      <c r="A193" s="6">
+        <v>202609040811</v>
+      </c>
+      <c r="B193" s="6">
+        <v>5</v>
+      </c>
+      <c r="C193" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="D193" s="6">
+        <v>57.5</v>
+      </c>
+      <c r="E193" s="6">
+        <v>12.7</v>
+      </c>
+      <c r="F193" s="6">
+        <v>16</v>
+      </c>
+      <c r="G193" s="7">
+        <v>92</v>
+      </c>
+      <c r="H193" s="6">
+        <v>37</v>
+      </c>
+      <c r="I193" s="7">
+        <v>95</v>
+      </c>
+      <c r="J193" s="6">
+        <v>77</v>
+      </c>
+      <c r="K193"/>
+      <c r="L193"/>
+      <c r="M193"/>
+      <c r="N193" s="6">
+        <v>13</v>
+      </c>
+      <c r="O193" s="6">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15">
+      <c r="A194" s="6">
+        <v>202609040811</v>
+      </c>
+      <c r="B194" s="6">
+        <v>6</v>
+      </c>
+      <c r="C194" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="D194" s="6">
+        <v>57</v>
+      </c>
+      <c r="E194" s="6">
+        <v>19.9</v>
+      </c>
+      <c r="F194" s="6">
+        <v>24</v>
+      </c>
+      <c r="G194" s="7">
+        <v>102</v>
+      </c>
+      <c r="H194" s="6">
+        <v>-3</v>
+      </c>
+      <c r="I194" s="7">
+        <v>97</v>
+      </c>
+      <c r="J194" s="6">
+        <v>58</v>
+      </c>
+      <c r="K194" s="6">
+        <v>1</v>
+      </c>
+      <c r="L194"/>
+      <c r="M194" s="6">
+        <v>1</v>
+      </c>
+      <c r="N194" s="6">
+        <v>2</v>
+      </c>
+      <c r="O194" s="6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15">
+      <c r="A195" s="6">
+        <v>202609040811</v>
+      </c>
+      <c r="B195" s="6">
+        <v>7</v>
+      </c>
+      <c r="C195" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D195" s="6">
+        <v>55</v>
+      </c>
+      <c r="E195" s="6">
+        <v>5.3</v>
+      </c>
+      <c r="F195" s="6">
+        <v>8</v>
+      </c>
+      <c r="G195" s="7">
+        <v>90</v>
+      </c>
+      <c r="H195" s="6">
+        <v>3</v>
+      </c>
+      <c r="I195" s="7">
+        <v>86</v>
+      </c>
+      <c r="J195" s="6">
+        <v>-160</v>
+      </c>
+      <c r="K195"/>
+      <c r="L195"/>
+      <c r="M195"/>
+      <c r="N195" s="6">
+        <v>15</v>
+      </c>
+      <c r="O195" s="6">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15">
+      <c r="A196" s="6">
+        <v>202609040811</v>
+      </c>
+      <c r="B196" s="6">
+        <v>8</v>
+      </c>
+      <c r="C196" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D196" s="6">
+        <v>55</v>
+      </c>
+      <c r="E196" s="6">
+        <v>15.5</v>
+      </c>
+      <c r="F196" s="6">
+        <v>16</v>
+      </c>
+      <c r="G196" s="7">
+        <v>101</v>
+      </c>
+      <c r="H196" s="6">
+        <v>75</v>
+      </c>
+      <c r="I196" s="7">
+        <v>87</v>
+      </c>
+      <c r="J196" s="6">
+        <v>36</v>
+      </c>
+      <c r="K196" s="6">
+        <v>1</v>
+      </c>
+      <c r="L196"/>
+      <c r="M196"/>
+      <c r="N196" s="6">
+        <v>4</v>
+      </c>
+      <c r="O196" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15">
+      <c r="A197" s="6">
+        <v>202609040811</v>
+      </c>
+      <c r="B197" s="6">
+        <v>9</v>
+      </c>
+      <c r="C197" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="D197" s="6">
+        <v>57</v>
+      </c>
+      <c r="E197" s="6">
+        <v>4.9</v>
+      </c>
+      <c r="F197" s="6">
+        <v>8</v>
+      </c>
+      <c r="G197" s="7">
+        <v>86</v>
+      </c>
+      <c r="H197" s="6">
+        <v>-210</v>
+      </c>
+      <c r="I197" s="7">
+        <v>83</v>
+      </c>
+      <c r="J197" s="6">
+        <v>-97</v>
+      </c>
+      <c r="K197"/>
+      <c r="L197"/>
+      <c r="M197" s="6">
+        <v>1</v>
+      </c>
+      <c r="N197" s="6">
+        <v>14</v>
+      </c>
+      <c r="O197" s="6">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15">
+      <c r="A198" s="6">
+        <v>202609040811</v>
+      </c>
+      <c r="B198" s="6">
+        <v>10</v>
+      </c>
+      <c r="C198" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D198" s="6">
+        <v>56</v>
+      </c>
+      <c r="E198" s="6">
+        <v>28.4</v>
+      </c>
+      <c r="F198" s="6">
+        <v>22</v>
+      </c>
+      <c r="G198" s="7">
+        <v>88</v>
+      </c>
+      <c r="H198" s="6">
+        <v>-5</v>
+      </c>
+      <c r="I198" s="7">
+        <v>95</v>
+      </c>
+      <c r="J198" s="6">
+        <v>-20</v>
+      </c>
+      <c r="K198"/>
+      <c r="L198"/>
+      <c r="M198"/>
+      <c r="N198" s="6">
+        <v>3</v>
+      </c>
+      <c r="O198" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15">
+      <c r="A199" s="6">
+        <v>202609040811</v>
+      </c>
+      <c r="B199" s="6">
+        <v>11</v>
+      </c>
+      <c r="C199" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D199" s="6">
+        <v>58.5</v>
+      </c>
+      <c r="E199" s="6">
+        <v>40</v>
+      </c>
+      <c r="F199" s="6">
+        <v>28</v>
+      </c>
+      <c r="G199" s="7">
+        <v>95</v>
+      </c>
+      <c r="H199" s="6">
+        <v>-40</v>
+      </c>
+      <c r="I199" s="7">
+        <v>102</v>
+      </c>
+      <c r="J199" s="6">
+        <v>59</v>
+      </c>
+      <c r="K199"/>
+      <c r="L199"/>
+      <c r="M199"/>
+      <c r="N199" s="6">
+        <v>8</v>
+      </c>
+      <c r="O199" s="6">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15">
+      <c r="A200" s="6">
+        <v>202609040811</v>
+      </c>
+      <c r="B200" s="6">
+        <v>12</v>
+      </c>
+      <c r="C200" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="D200" s="6">
+        <v>55</v>
+      </c>
+      <c r="E200" s="6">
+        <v>10.8</v>
+      </c>
+      <c r="F200" s="6">
+        <v>15</v>
+      </c>
+      <c r="G200" s="7">
+        <v>104</v>
+      </c>
+      <c r="H200" s="6">
+        <v>70</v>
+      </c>
+      <c r="I200" s="7">
+        <v>100</v>
+      </c>
+      <c r="J200" s="6">
+        <v>65</v>
+      </c>
+      <c r="K200"/>
+      <c r="L200"/>
+      <c r="M200"/>
+      <c r="N200" s="6">
+        <v>5</v>
+      </c>
+      <c r="O200" s="6">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15">
+      <c r="A201" s="6">
+        <v>202609040811</v>
+      </c>
+      <c r="B201" s="6">
+        <v>13</v>
+      </c>
+      <c r="C201" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="D201" s="6">
+        <v>59</v>
+      </c>
+      <c r="E201" s="6">
+        <v>53.7</v>
+      </c>
+      <c r="F201" s="6">
+        <v>44</v>
+      </c>
+      <c r="G201" s="7">
+        <v>119</v>
+      </c>
+      <c r="H201" s="6">
+        <v>-3</v>
+      </c>
+      <c r="I201" s="7">
+        <v>105</v>
+      </c>
+      <c r="J201" s="6">
+        <v>-4</v>
+      </c>
+      <c r="K201"/>
+      <c r="L201"/>
+      <c r="M201"/>
+      <c r="N201" s="6">
+        <v>1</v>
+      </c>
+      <c r="O201" s="6">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15">
+      <c r="A202" s="6">
+        <v>202609040811</v>
+      </c>
+      <c r="B202" s="6">
+        <v>14</v>
+      </c>
+      <c r="C202" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="D202" s="6">
+        <v>57</v>
+      </c>
+      <c r="E202" s="6">
+        <v>31.9</v>
+      </c>
+      <c r="F202" s="6">
+        <v>23</v>
+      </c>
+      <c r="G202" s="7">
+        <v>106</v>
+      </c>
+      <c r="H202" s="6">
+        <v>66</v>
+      </c>
+      <c r="I202" s="7">
+        <v>98</v>
+      </c>
+      <c r="J202" s="6">
+        <v>18</v>
+      </c>
+      <c r="K202"/>
+      <c r="L202"/>
+      <c r="M202"/>
+      <c r="N202" s="6">
+        <v>6</v>
+      </c>
+      <c r="O202" s="6">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15">
+      <c r="A203" s="6">
+        <v>202609040811</v>
+      </c>
+      <c r="B203" s="6">
+        <v>15</v>
+      </c>
+      <c r="C203" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D203" s="6">
+        <v>58</v>
+      </c>
+      <c r="E203" s="6">
+        <v>24.7</v>
+      </c>
+      <c r="F203" s="6">
+        <v>28</v>
+      </c>
+      <c r="G203" s="7">
+        <v>90</v>
+      </c>
+      <c r="H203" s="6">
+        <v>42</v>
+      </c>
+      <c r="I203" s="7">
+        <v>115</v>
+      </c>
+      <c r="J203" s="6">
+        <v>-63</v>
+      </c>
+      <c r="K203"/>
+      <c r="L203"/>
+      <c r="M203"/>
+      <c r="N203" s="6">
+        <v>12</v>
+      </c>
+      <c r="O203" s="6">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15">
+      <c r="A204" s="6">
+        <v>202609040811</v>
+      </c>
+      <c r="B204" s="6">
+        <v>16</v>
+      </c>
+      <c r="C204" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D204" s="6">
+        <v>54</v>
+      </c>
+      <c r="E204" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="F204" s="6">
+        <v>1</v>
+      </c>
+      <c r="G204"/>
+      <c r="H204"/>
+      <c r="I204"/>
+      <c r="J204"/>
+      <c r="K204"/>
+      <c r="L204"/>
+      <c r="M204"/>
+      <c r="N204" s="6">
+        <v>10</v>
+      </c>
+      <c r="O204" s="6">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15">
+      <c r="A205"/>
+      <c r="B205"/>
+      <c r="C205"/>
+      <c r="D205"/>
+      <c r="E205"/>
+      <c r="F205"/>
+      <c r="G205"/>
+      <c r="H205"/>
+      <c r="I205"/>
+      <c r="J205"/>
+      <c r="K205"/>
+      <c r="L205"/>
+      <c r="M205"/>
+      <c r="N205"/>
+      <c r="O205"/>
+    </row>
+    <row r="206" spans="1:15">
+      <c r="A206"/>
+      <c r="B206"/>
+      <c r="C206"/>
+      <c r="D206"/>
+      <c r="E206"/>
+      <c r="F206"/>
+      <c r="G206"/>
+      <c r="H206"/>
+      <c r="I206"/>
+      <c r="J206"/>
+      <c r="K206"/>
+      <c r="L206"/>
+      <c r="M206"/>
+      <c r="N206"/>
+      <c r="O206"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
